--- a/src/downloads/tubes-film-budget-template.xlsx
+++ b/src/downloads/tubes-film-budget-template.xlsx
@@ -160,7 +160,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">Film budget template</t>
+          <t xml:space="preserve">Tubes Production Budget</t>
         </is>
       </c>
     </row>
@@ -168,12 +168,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Version: Film budget template</t>
+          <t xml:space="preserve">Version: Tubes Production Budget</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Date: 17 September 2026</t>
+          <t xml:space="preserve">Date: 23 October 2026</t>
         </is>
       </c>
     </row>
@@ -192,7 +192,7 @@
         </is>
       </c>
       <c r="B6" s="4">
-        <f>G387</f>
+        <f>G378</f>
         <v>0</v>
       </c>
     </row>
@@ -203,7 +203,7 @@
         </is>
       </c>
       <c r="B7" s="4">
-        <f>G388</f>
+        <f>G379</f>
         <v>0</v>
       </c>
     </row>
@@ -214,7 +214,7 @@
         </is>
       </c>
       <c r="B8" s="4">
-        <f>G389</f>
+        <f>G380</f>
         <v>0</v>
       </c>
     </row>
@@ -260,7 +260,7 @@
     <row r="12">
       <c r="A12" s="7" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100 - Development, Story, Rights, Continuity</t>
+          <t xml:space="preserve">0100 - Development &amp; Research</t>
         </is>
       </c>
       <c r="B12" s="7"/>
@@ -273,12 +273,12 @@
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1102</t>
+          <t xml:space="preserve">0103</t>
         </is>
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Development</t>
+          <t xml:space="preserve">Concept development</t>
         </is>
       </c>
       <c r="C13" s="8"/>
@@ -297,12 +297,12 @@
     <row r="14">
       <c r="A14" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104</t>
+          <t xml:space="preserve">0106</t>
         </is>
       </c>
       <c r="B14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Script &amp; Development</t>
+          <t xml:space="preserve">Screenplay writing</t>
         </is>
       </c>
       <c r="C14" s="8"/>
@@ -321,12 +321,12 @@
     <row r="15">
       <c r="A15" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1109</t>
+          <t xml:space="preserve">0109</t>
         </is>
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Script Coord</t>
+          <t xml:space="preserve">Script editing</t>
         </is>
       </c>
       <c r="C15" s="8"/>
@@ -345,12 +345,12 @@
     <row r="16">
       <c r="A16" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1111</t>
+          <t xml:space="preserve">0112</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Research</t>
+          <t xml:space="preserve">Research and fact checking</t>
         </is>
       </c>
       <c r="C16" s="8"/>
@@ -369,12 +369,12 @@
     <row r="17">
       <c r="A17" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1114</t>
+          <t xml:space="preserve">0115</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Script Copies</t>
+          <t xml:space="preserve">Development producer</t>
         </is>
       </c>
       <c r="C17" s="8"/>
@@ -393,12 +393,12 @@
     <row r="18">
       <c r="A18" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1177</t>
+          <t xml:space="preserve">0118</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writers Meals, Per Diems</t>
+          <t xml:space="preserve">Development travel</t>
         </is>
       </c>
       <c r="C18" s="8"/>
@@ -417,12 +417,12 @@
     <row r="19">
       <c r="A19" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180</t>
+          <t xml:space="preserve">0121</t>
         </is>
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writers Airfare</t>
+          <t xml:space="preserve">Pitch and presentation materials</t>
         </is>
       </c>
       <c r="C19" s="8"/>
@@ -439,38 +439,27 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1185</t>
-        </is>
-      </c>
-      <c r="B20" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Writers Hotel</t>
-        </is>
-      </c>
-      <c r="C20" s="8"/>
-      <c r="D20" s="9">
-        <v>0</v>
-      </c>
-      <c r="E20" s="11"/>
-      <c r="F20" s="10">
-        <v>0</v>
-      </c>
-      <c r="G20" s="10">
-        <f>ROUND(D20*F20,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A20" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0200 - Rights, Clearances &amp; Archive</t>
+        </is>
+      </c>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="7"/>
     </row>
     <row r="21">
       <c r="A21" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186</t>
+          <t xml:space="preserve">0203</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Writers Transport</t>
+          <t xml:space="preserve">Underlying rights</t>
         </is>
       </c>
       <c r="C21" s="8"/>
@@ -487,27 +476,38 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1200 - Producers</t>
-        </is>
-      </c>
-      <c r="B22" s="7"/>
-      <c r="C22" s="7"/>
-      <c r="D22" s="7"/>
-      <c r="E22" s="7"/>
-      <c r="F22" s="7"/>
-      <c r="G22" s="7"/>
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0206</t>
+        </is>
+      </c>
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Writer options and agreements</t>
+        </is>
+      </c>
+      <c r="C22" s="8"/>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="11"/>
+      <c r="F22" s="10">
+        <v>0</v>
+      </c>
+      <c r="G22" s="10">
+        <f>ROUND(D22*F22,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201</t>
+          <t xml:space="preserve">0209</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producers</t>
+          <t xml:space="preserve">Music research clearance</t>
         </is>
       </c>
       <c r="C23" s="8"/>
@@ -526,12 +526,12 @@
     <row r="24">
       <c r="A24" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202</t>
+          <t xml:space="preserve">0212</t>
         </is>
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Executive Producer</t>
+          <t xml:space="preserve">Archive research</t>
         </is>
       </c>
       <c r="C24" s="8"/>
@@ -550,12 +550,12 @@
     <row r="25">
       <c r="A25" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1205</t>
+          <t xml:space="preserve">0215</t>
         </is>
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Co-Producer</t>
+          <t xml:space="preserve">Archive footage licences</t>
         </is>
       </c>
       <c r="C25" s="8"/>
@@ -574,12 +574,12 @@
     <row r="26">
       <c r="A26" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206</t>
+          <t xml:space="preserve">0218</t>
         </is>
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Line Producer</t>
+          <t xml:space="preserve">Artwork and brand clearances</t>
         </is>
       </c>
       <c r="C26" s="8"/>
@@ -598,12 +598,12 @@
     <row r="27">
       <c r="A27" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208</t>
+          <t xml:space="preserve">0221</t>
         </is>
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Associate Producer</t>
+          <t xml:space="preserve">Script legal review</t>
         </is>
       </c>
       <c r="C27" s="8"/>
@@ -622,12 +622,12 @@
     <row r="28">
       <c r="A28" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212</t>
+          <t xml:space="preserve">0224</t>
         </is>
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producers Asst</t>
+          <t xml:space="preserve">Chain of title documentation</t>
         </is>
       </c>
       <c r="C28" s="8"/>
@@ -644,38 +644,27 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1213</t>
-        </is>
-      </c>
-      <c r="B29" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entertainment</t>
-        </is>
-      </c>
-      <c r="C29" s="8"/>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-      <c r="E29" s="11"/>
-      <c r="F29" s="10">
-        <v>0</v>
-      </c>
-      <c r="G29" s="10">
-        <f>ROUND(D29*F29,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A29" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0300 - Producing &amp; Business Affairs</t>
+        </is>
+      </c>
+      <c r="B29" s="7"/>
+      <c r="C29" s="7"/>
+      <c r="D29" s="7"/>
+      <c r="E29" s="7"/>
+      <c r="F29" s="7"/>
+      <c r="G29" s="7"/>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214</t>
+          <t xml:space="preserve">0303</t>
         </is>
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Lead producer</t>
         </is>
       </c>
       <c r="C30" s="8"/>
@@ -694,12 +683,12 @@
     <row r="31">
       <c r="A31" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235</t>
+          <t xml:space="preserve">0306</t>
         </is>
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Materials &amp; Supplies</t>
+          <t xml:space="preserve">Executive producer</t>
         </is>
       </c>
       <c r="C31" s="8"/>
@@ -716,27 +705,38 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1300 - Direction</t>
-        </is>
-      </c>
-      <c r="B32" s="7"/>
-      <c r="C32" s="7"/>
-      <c r="D32" s="7"/>
-      <c r="E32" s="7"/>
-      <c r="F32" s="7"/>
-      <c r="G32" s="7"/>
+      <c r="A32" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0309</t>
+        </is>
+      </c>
+      <c r="B32" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Co-producer</t>
+        </is>
+      </c>
+      <c r="C32" s="8"/>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="11"/>
+      <c r="F32" s="10">
+        <v>0</v>
+      </c>
+      <c r="G32" s="10">
+        <f>ROUND(D32*F32,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1301</t>
+          <t xml:space="preserve">0312</t>
         </is>
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director</t>
+          <t xml:space="preserve">Line producer</t>
         </is>
       </c>
       <c r="C33" s="8"/>
@@ -755,12 +755,12 @@
     <row r="34">
       <c r="A34" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1302</t>
+          <t xml:space="preserve">0315</t>
         </is>
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director's Assistant</t>
+          <t xml:space="preserve">Associate producer</t>
         </is>
       </c>
       <c r="C34" s="8"/>
@@ -779,12 +779,12 @@
     <row r="35">
       <c r="A35" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1303</t>
+          <t xml:space="preserve">0318</t>
         </is>
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Technical Advisor</t>
+          <t xml:space="preserve">Business affairs producer</t>
         </is>
       </c>
       <c r="C35" s="8"/>
@@ -803,12 +803,12 @@
     <row r="36">
       <c r="A36" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1304</t>
+          <t xml:space="preserve">0321</t>
         </is>
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dialogue Coach</t>
+          <t xml:space="preserve">Producer assistant</t>
         </is>
       </c>
       <c r="C36" s="8"/>
@@ -827,12 +827,12 @@
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1305</t>
+          <t xml:space="preserve">0324</t>
         </is>
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd Unit Director</t>
+          <t xml:space="preserve">Producer office and supplies</t>
         </is>
       </c>
       <c r="C37" s="8"/>
@@ -849,38 +849,27 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1306</t>
-        </is>
-      </c>
-      <c r="B38" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Purchases &amp; Rentals</t>
-        </is>
-      </c>
-      <c r="C38" s="8"/>
-      <c r="D38" s="9">
-        <v>0</v>
-      </c>
-      <c r="E38" s="11"/>
-      <c r="F38" s="10">
-        <v>0</v>
-      </c>
-      <c r="G38" s="10">
-        <f>ROUND(D38*F38,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A38" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0400 - Directing &amp; Creative Leadership</t>
+        </is>
+      </c>
+      <c r="B38" s="7"/>
+      <c r="C38" s="7"/>
+      <c r="D38" s="7"/>
+      <c r="E38" s="7"/>
+      <c r="F38" s="7"/>
+      <c r="G38" s="7"/>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307</t>
+          <t xml:space="preserve">0403</t>
         </is>
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Entertainment</t>
+          <t xml:space="preserve">Director</t>
         </is>
       </c>
       <c r="C39" s="8"/>
@@ -897,27 +886,38 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1400 - Cast</t>
-        </is>
-      </c>
-      <c r="B40" s="7"/>
-      <c r="C40" s="7"/>
-      <c r="D40" s="7"/>
-      <c r="E40" s="7"/>
-      <c r="F40" s="7"/>
-      <c r="G40" s="7"/>
+      <c r="A40" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0406</t>
+        </is>
+      </c>
+      <c r="B40" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Director assistant</t>
+        </is>
+      </c>
+      <c r="C40" s="8"/>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="11"/>
+      <c r="F40" s="10">
+        <v>0</v>
+      </c>
+      <c r="G40" s="10">
+        <f>ROUND(D40*F40,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1401</t>
+          <t xml:space="preserve">0409</t>
         </is>
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stars &amp; Leads</t>
+          <t xml:space="preserve">Creative consultant</t>
         </is>
       </c>
       <c r="C41" s="8"/>
@@ -936,12 +936,12 @@
     <row r="42">
       <c r="A42" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1402</t>
+          <t xml:space="preserve">0412</t>
         </is>
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Support Cast</t>
+          <t xml:space="preserve">Technical adviser</t>
         </is>
       </c>
       <c r="C42" s="8"/>
@@ -960,12 +960,12 @@
     <row r="43">
       <c r="A43" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1403</t>
+          <t xml:space="preserve">0415</t>
         </is>
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Day Players</t>
+          <t xml:space="preserve">Dialogue and dialect coaching</t>
         </is>
       </c>
       <c r="C43" s="8"/>
@@ -984,12 +984,12 @@
     <row r="44">
       <c r="A44" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1404</t>
+          <t xml:space="preserve">0418</t>
         </is>
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cast Perks</t>
+          <t xml:space="preserve">Storyboarding</t>
         </is>
       </c>
       <c r="C44" s="8"/>
@@ -1008,12 +1008,12 @@
     <row r="45">
       <c r="A45" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1405</t>
+          <t xml:space="preserve">0421</t>
         </is>
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Musicians</t>
+          <t xml:space="preserve">Creative reference materials</t>
         </is>
       </c>
       <c r="C45" s="8"/>
@@ -1030,38 +1030,27 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1411</t>
-        </is>
-      </c>
-      <c r="B46" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Overtime</t>
-        </is>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="D46" s="9">
-        <v>0</v>
-      </c>
-      <c r="E46" s="11"/>
-      <c r="F46" s="10">
-        <v>0</v>
-      </c>
-      <c r="G46" s="10">
-        <f>ROUND(D46*F46,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0500 - Cast, Casting &amp; Performance</t>
+        </is>
+      </c>
+      <c r="B46" s="7"/>
+      <c r="C46" s="7"/>
+      <c r="D46" s="7"/>
+      <c r="E46" s="7"/>
+      <c r="F46" s="7"/>
+      <c r="G46" s="7"/>
     </row>
     <row r="47">
       <c r="A47" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1417</t>
+          <t xml:space="preserve">0503</t>
         </is>
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Looping</t>
+          <t xml:space="preserve">Principal cast</t>
         </is>
       </c>
       <c r="C47" s="8"/>
@@ -1080,12 +1069,12 @@
     <row r="48">
       <c r="A48" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420</t>
+          <t xml:space="preserve">0506</t>
         </is>
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Coordinator</t>
+          <t xml:space="preserve">Supporting cast</t>
         </is>
       </c>
       <c r="C48" s="8"/>
@@ -1104,12 +1093,12 @@
     <row r="49">
       <c r="A49" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1421</t>
+          <t xml:space="preserve">0509</t>
         </is>
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Players</t>
+          <t xml:space="preserve">Day performers</t>
         </is>
       </c>
       <c r="C49" s="8"/>
@@ -1128,12 +1117,12 @@
     <row r="50">
       <c r="A50" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1422</t>
+          <t xml:space="preserve">0512</t>
         </is>
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Adjustments</t>
+          <t xml:space="preserve">Voice performers</t>
         </is>
       </c>
       <c r="C50" s="8"/>
@@ -1152,12 +1141,12 @@
     <row r="51">
       <c r="A51" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1423</t>
+          <t xml:space="preserve">0515</t>
         </is>
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Purchases/Rentals</t>
+          <t xml:space="preserve">Presenters and contributors</t>
         </is>
       </c>
       <c r="C51" s="8"/>
@@ -1176,12 +1165,12 @@
     <row r="52">
       <c r="A52" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1430</t>
+          <t xml:space="preserve">0518</t>
         </is>
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casting Director</t>
+          <t xml:space="preserve">Casting director</t>
         </is>
       </c>
       <c r="C52" s="8"/>
@@ -1200,12 +1189,12 @@
     <row r="53">
       <c r="A53" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431</t>
+          <t xml:space="preserve">0521</t>
         </is>
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casting Associate</t>
+          <t xml:space="preserve">Casting associate</t>
         </is>
       </c>
       <c r="C53" s="8"/>
@@ -1224,12 +1213,12 @@
     <row r="54">
       <c r="A54" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1433</t>
+          <t xml:space="preserve">0524</t>
         </is>
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Casting Expenses</t>
+          <t xml:space="preserve">Auditions and self-tape platform</t>
         </is>
       </c>
       <c r="C54" s="8"/>
@@ -1248,12 +1237,12 @@
     <row r="55">
       <c r="A55" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1434</t>
+          <t xml:space="preserve">0527</t>
         </is>
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Open Musical Casting</t>
+          <t xml:space="preserve">Rehearsals and read-throughs</t>
         </is>
       </c>
       <c r="C55" s="8"/>
@@ -1272,12 +1261,12 @@
     <row r="56">
       <c r="A56" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1459</t>
+          <t xml:space="preserve">0530</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dialogue Coach</t>
+          <t xml:space="preserve">Cast coaching</t>
         </is>
       </c>
       <c r="C56" s="8"/>
@@ -1296,12 +1285,12 @@
     <row r="57">
       <c r="A57" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1460</t>
+          <t xml:space="preserve">0533</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Welfare Worker/Teacher</t>
+          <t xml:space="preserve">Cast fittings and tests</t>
         </is>
       </c>
       <c r="C57" s="8"/>
@@ -1318,51 +1307,51 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1500 - ATL Travel &amp; Living</t>
-        </is>
-      </c>
-      <c r="B58" s="7"/>
-      <c r="C58" s="7"/>
-      <c r="D58" s="7"/>
-      <c r="E58" s="7"/>
-      <c r="F58" s="7"/>
-      <c r="G58" s="7"/>
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0536</t>
+        </is>
+      </c>
+      <c r="B58" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Child performer support</t>
+        </is>
+      </c>
+      <c r="C58" s="8"/>
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="11"/>
+      <c r="F58" s="10">
+        <v>0</v>
+      </c>
+      <c r="G58" s="10">
+        <f>ROUND(D58*F58,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1520</t>
-        </is>
-      </c>
-      <c r="B59" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Producer's Airfare</t>
-        </is>
-      </c>
-      <c r="C59" s="8"/>
-      <c r="D59" s="9">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11"/>
-      <c r="F59" s="10">
-        <v>0</v>
-      </c>
-      <c r="G59" s="10">
-        <f>ROUND(D59*F59,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A59" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0600 - Production Management &amp; Accounts</t>
+        </is>
+      </c>
+      <c r="B59" s="7"/>
+      <c r="C59" s="7"/>
+      <c r="D59" s="7"/>
+      <c r="E59" s="7"/>
+      <c r="F59" s="7"/>
+      <c r="G59" s="7"/>
     </row>
     <row r="60">
       <c r="A60" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1521</t>
+          <t xml:space="preserve">0603</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producer's Hotel</t>
+          <t xml:space="preserve">Production manager</t>
         </is>
       </c>
       <c r="C60" s="8"/>
@@ -1381,12 +1370,12 @@
     <row r="61">
       <c r="A61" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1522</t>
+          <t xml:space="preserve">0606</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producer's Per Diem</t>
+          <t xml:space="preserve">Production coordinator</t>
         </is>
       </c>
       <c r="C61" s="8"/>
@@ -1405,12 +1394,12 @@
     <row r="62">
       <c r="A62" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1523</t>
+          <t xml:space="preserve">0609</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Producer Transport</t>
+          <t xml:space="preserve">Production secretary</t>
         </is>
       </c>
       <c r="C62" s="8"/>
@@ -1429,12 +1418,12 @@
     <row r="63">
       <c r="A63" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1530</t>
+          <t xml:space="preserve">0612</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director's Airfare</t>
+          <t xml:space="preserve">Production assistants</t>
         </is>
       </c>
       <c r="C63" s="8"/>
@@ -1453,12 +1442,12 @@
     <row r="64">
       <c r="A64" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531</t>
+          <t xml:space="preserve">0615</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director's Hotel</t>
+          <t xml:space="preserve">Production accountant</t>
         </is>
       </c>
       <c r="C64" s="8"/>
@@ -1477,12 +1466,12 @@
     <row r="65">
       <c r="A65" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1532</t>
+          <t xml:space="preserve">0618</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director's Per Diem</t>
+          <t xml:space="preserve">Assistant production accountant</t>
         </is>
       </c>
       <c r="C65" s="8"/>
@@ -1501,12 +1490,12 @@
     <row r="66">
       <c r="A66" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1533</t>
+          <t xml:space="preserve">0621</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director's Transport</t>
+          <t xml:space="preserve">Payroll accountant</t>
         </is>
       </c>
       <c r="C66" s="8"/>
@@ -1525,12 +1514,12 @@
     <row r="67">
       <c r="A67" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1540</t>
+          <t xml:space="preserve">0624</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cast Airfare</t>
+          <t xml:space="preserve">Cashier and petty cash support</t>
         </is>
       </c>
       <c r="C67" s="8"/>
@@ -1549,12 +1538,12 @@
     <row r="68">
       <c r="A68" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1541</t>
+          <t xml:space="preserve">0627</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cast Hotel</t>
+          <t xml:space="preserve">Cost reporting support</t>
         </is>
       </c>
       <c r="C68" s="8"/>
@@ -1573,12 +1562,12 @@
     <row r="69">
       <c r="A69" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1542</t>
+          <t xml:space="preserve">0630</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cast Per Diem</t>
+          <t xml:space="preserve">Production office supplies</t>
         </is>
       </c>
       <c r="C69" s="8"/>
@@ -1595,38 +1584,27 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1543</t>
-        </is>
-      </c>
-      <c r="B70" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Cast Transport</t>
-        </is>
-      </c>
-      <c r="C70" s="8"/>
-      <c r="D70" s="9">
-        <v>0</v>
-      </c>
-      <c r="E70" s="11"/>
-      <c r="F70" s="10">
-        <v>0</v>
-      </c>
-      <c r="G70" s="10">
-        <f>ROUND(D70*F70,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A70" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0700 - Assistant Direction, Continuity &amp; Background</t>
+        </is>
+      </c>
+      <c r="B70" s="7"/>
+      <c r="C70" s="7"/>
+      <c r="D70" s="7"/>
+      <c r="E70" s="7"/>
+      <c r="F70" s="7"/>
+      <c r="G70" s="7"/>
     </row>
     <row r="71">
       <c r="A71" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1590</t>
+          <t xml:space="preserve">0703</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Airfare</t>
+          <t xml:space="preserve">First assistant director</t>
         </is>
       </c>
       <c r="C71" s="8"/>
@@ -1645,12 +1623,12 @@
     <row r="72">
       <c r="A72" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1591</t>
+          <t xml:space="preserve">0706</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Hotel</t>
+          <t xml:space="preserve">Second assistant director</t>
         </is>
       </c>
       <c r="C72" s="8"/>
@@ -1669,12 +1647,12 @@
     <row r="73">
       <c r="A73" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">1592</t>
+          <t xml:space="preserve">0709</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stunt Per Diem</t>
+          <t xml:space="preserve">Third assistant director</t>
         </is>
       </c>
       <c r="C73" s="8"/>
@@ -1691,27 +1669,38 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2000 - Production Staff</t>
-        </is>
-      </c>
-      <c r="B74" s="7"/>
-      <c r="C74" s="7"/>
-      <c r="D74" s="7"/>
-      <c r="E74" s="7"/>
-      <c r="F74" s="7"/>
-      <c r="G74" s="7"/>
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0712</t>
+        </is>
+      </c>
+      <c r="B74" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Floor runners</t>
+        </is>
+      </c>
+      <c r="C74" s="8"/>
+      <c r="D74" s="9">
+        <v>0</v>
+      </c>
+      <c r="E74" s="11"/>
+      <c r="F74" s="10">
+        <v>0</v>
+      </c>
+      <c r="G74" s="10">
+        <f>ROUND(D74*F74,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2001</t>
+          <t xml:space="preserve">0715</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Manager</t>
+          <t xml:space="preserve">Script supervisor</t>
         </is>
       </c>
       <c r="C75" s="8"/>
@@ -1730,12 +1719,12 @@
     <row r="76">
       <c r="A76" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2002</t>
+          <t xml:space="preserve">0718</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">First Assistant Director</t>
+          <t xml:space="preserve">Background casting</t>
         </is>
       </c>
       <c r="C76" s="8"/>
@@ -1754,12 +1743,12 @@
     <row r="77">
       <c r="A77" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2003</t>
+          <t xml:space="preserve">0721</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Assistant Director</t>
+          <t xml:space="preserve">Background performers</t>
         </is>
       </c>
       <c r="C77" s="8"/>
@@ -1778,12 +1767,12 @@
     <row r="78">
       <c r="A78" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2004</t>
+          <t xml:space="preserve">0724</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Third Assistant Director</t>
+          <t xml:space="preserve">Stand-ins and doubles</t>
         </is>
       </c>
       <c r="C78" s="8"/>
@@ -1802,12 +1791,12 @@
     <row r="79">
       <c r="A79" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2005</t>
+          <t xml:space="preserve">0727</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Script Supervisor</t>
+          <t xml:space="preserve">Crowd coordination</t>
         </is>
       </c>
       <c r="C79" s="8"/>
@@ -1826,12 +1815,12 @@
     <row r="80">
       <c r="A80" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2007</t>
+          <t xml:space="preserve">0730</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location Manager</t>
+          <t xml:space="preserve">Chaperones and tutors</t>
         </is>
       </c>
       <c r="C80" s="8"/>
@@ -1848,38 +1837,27 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2008</t>
-        </is>
-      </c>
-      <c r="B81" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unit &amp; Asst Location Manager</t>
-        </is>
-      </c>
-      <c r="C81" s="8"/>
-      <c r="D81" s="9">
-        <v>0</v>
-      </c>
-      <c r="E81" s="11"/>
-      <c r="F81" s="10">
-        <v>0</v>
-      </c>
-      <c r="G81" s="10">
-        <f>ROUND(D81*F81,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A81" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0800 - Locations, Permits &amp; Site Services</t>
+        </is>
+      </c>
+      <c r="B81" s="7"/>
+      <c r="C81" s="7"/>
+      <c r="D81" s="7"/>
+      <c r="E81" s="7"/>
+      <c r="F81" s="7"/>
+      <c r="G81" s="7"/>
     </row>
     <row r="82">
       <c r="A82" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2009</t>
+          <t xml:space="preserve">0803</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Coordinator</t>
+          <t xml:space="preserve">Location manager</t>
         </is>
       </c>
       <c r="C82" s="8"/>
@@ -1898,12 +1876,12 @@
     <row r="83">
       <c r="A83" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2010</t>
+          <t xml:space="preserve">0806</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Production Coordinator</t>
+          <t xml:space="preserve">Assistant location manager</t>
         </is>
       </c>
       <c r="C83" s="8"/>
@@ -1922,12 +1900,12 @@
     <row r="84">
       <c r="A84" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2011</t>
+          <t xml:space="preserve">0809</t>
         </is>
       </c>
       <c r="B84" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Office Assistants</t>
+          <t xml:space="preserve">Location scouting</t>
         </is>
       </c>
       <c r="C84" s="8"/>
@@ -1946,12 +1924,12 @@
     <row r="85">
       <c r="A85" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2012</t>
+          <t xml:space="preserve">0812</t>
         </is>
       </c>
       <c r="B85" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set Pas</t>
+          <t xml:space="preserve">Location hire</t>
         </is>
       </c>
       <c r="C85" s="8"/>
@@ -1970,12 +1948,12 @@
     <row r="86">
       <c r="A86" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2013</t>
+          <t xml:space="preserve">0815</t>
         </is>
       </c>
       <c r="B86" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Accountant</t>
+          <t xml:space="preserve">Filming permits</t>
         </is>
       </c>
       <c r="C86" s="8"/>
@@ -1994,12 +1972,12 @@
     <row r="87">
       <c r="A87" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2014</t>
+          <t xml:space="preserve">0818</t>
         </is>
       </c>
       <c r="B87" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Assistant Accountants</t>
+          <t xml:space="preserve">Resident and business liaison</t>
         </is>
       </c>
       <c r="C87" s="8"/>
@@ -2018,12 +1996,12 @@
     <row r="88">
       <c r="A88" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2015</t>
+          <t xml:space="preserve">0821</t>
         </is>
       </c>
       <c r="B88" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cashier/Accounts Trainee</t>
+          <t xml:space="preserve">Location security</t>
         </is>
       </c>
       <c r="C88" s="8"/>
@@ -2042,12 +2020,12 @@
     <row r="89">
       <c r="A89" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2017</t>
+          <t xml:space="preserve">0824</t>
         </is>
       </c>
       <c r="B89" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Computer/Box Rentals</t>
+          <t xml:space="preserve">Police and traffic control</t>
         </is>
       </c>
       <c r="C89" s="8"/>
@@ -2066,12 +2044,12 @@
     <row r="90">
       <c r="A90" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2020</t>
+          <t xml:space="preserve">0827</t>
         </is>
       </c>
       <c r="B90" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Miscellaneous</t>
+          <t xml:space="preserve">Technical parking and base camp</t>
         </is>
       </c>
       <c r="C90" s="8"/>
@@ -2088,51 +2066,51 @@
       </c>
     </row>
     <row r="91">
-      <c r="A91" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2100 - Extra Talent</t>
-        </is>
-      </c>
-      <c r="B91" s="7"/>
-      <c r="C91" s="7"/>
-      <c r="D91" s="7"/>
-      <c r="E91" s="7"/>
-      <c r="F91" s="7"/>
-      <c r="G91" s="7"/>
+      <c r="A91" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0830</t>
+        </is>
+      </c>
+      <c r="B91" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Location restoration</t>
+        </is>
+      </c>
+      <c r="C91" s="8"/>
+      <c r="D91" s="9">
+        <v>0</v>
+      </c>
+      <c r="E91" s="11"/>
+      <c r="F91" s="10">
+        <v>0</v>
+      </c>
+      <c r="G91" s="10">
+        <f>ROUND(D91*F91,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="92">
-      <c r="A92" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2101</t>
-        </is>
-      </c>
-      <c r="B92" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Stand-Ins</t>
-        </is>
-      </c>
-      <c r="C92" s="8"/>
-      <c r="D92" s="9">
-        <v>0</v>
-      </c>
-      <c r="E92" s="11"/>
-      <c r="F92" s="10">
-        <v>0</v>
-      </c>
-      <c r="G92" s="10">
-        <f>ROUND(D92*F92,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A92" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0900 - Travel, Accommodation &amp; Daily Allowances</t>
+        </is>
+      </c>
+      <c r="B92" s="7"/>
+      <c r="C92" s="7"/>
+      <c r="D92" s="7"/>
+      <c r="E92" s="7"/>
+      <c r="F92" s="7"/>
+      <c r="G92" s="7"/>
     </row>
     <row r="93">
       <c r="A93" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2103</t>
+          <t xml:space="preserve">0903</t>
         </is>
       </c>
       <c r="B93" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extras</t>
+          <t xml:space="preserve">Air travel</t>
         </is>
       </c>
       <c r="C93" s="8"/>
@@ -2151,12 +2129,12 @@
     <row r="94">
       <c r="A94" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110</t>
+          <t xml:space="preserve">0906</t>
         </is>
       </c>
       <c r="B94" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extras Casting Coordinator</t>
+          <t xml:space="preserve">Rail and ferry travel</t>
         </is>
       </c>
       <c r="C94" s="8"/>
@@ -2175,12 +2153,12 @@
     <row r="95">
       <c r="A95" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2115</t>
+          <t xml:space="preserve">0909</t>
         </is>
       </c>
       <c r="B95" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Chaperones</t>
+          <t xml:space="preserve">Hotels and accommodation</t>
         </is>
       </c>
       <c r="C95" s="8"/>
@@ -2199,12 +2177,12 @@
     <row r="96">
       <c r="A96" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2120</t>
+          <t xml:space="preserve">0912</t>
         </is>
       </c>
       <c r="B96" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extras Travel &amp; Living</t>
+          <t xml:space="preserve">Daily allowances</t>
         </is>
       </c>
       <c r="C96" s="8"/>
@@ -2223,12 +2201,12 @@
     <row r="97">
       <c r="A97" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2125</t>
+          <t xml:space="preserve">0915</t>
         </is>
       </c>
       <c r="B97" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Local taxis and transfers</t>
         </is>
       </c>
       <c r="C97" s="8"/>
@@ -2247,12 +2225,12 @@
     <row r="98">
       <c r="A98" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2130</t>
+          <t xml:space="preserve">0918</t>
         </is>
       </c>
       <c r="B98" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rental</t>
+          <t xml:space="preserve">Travel booking fees</t>
         </is>
       </c>
       <c r="C98" s="8"/>
@@ -2269,27 +2247,38 @@
       </c>
     </row>
     <row r="99">
-      <c r="A99" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2200 - Art Department</t>
-        </is>
-      </c>
-      <c r="B99" s="7"/>
-      <c r="C99" s="7"/>
-      <c r="D99" s="7"/>
-      <c r="E99" s="7"/>
-      <c r="F99" s="7"/>
-      <c r="G99" s="7"/>
+      <c r="A99" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">0921</t>
+        </is>
+      </c>
+      <c r="B99" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visas and travel documents</t>
+        </is>
+      </c>
+      <c r="C99" s="8"/>
+      <c r="D99" s="9">
+        <v>0</v>
+      </c>
+      <c r="E99" s="11"/>
+      <c r="F99" s="10">
+        <v>0</v>
+      </c>
+      <c r="G99" s="10">
+        <f>ROUND(D99*F99,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2201</t>
+          <t xml:space="preserve">0924</t>
         </is>
       </c>
       <c r="B100" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Designer</t>
+          <t xml:space="preserve">Baggage and freight excess</t>
         </is>
       </c>
       <c r="C100" s="8"/>
@@ -2306,38 +2295,27 @@
       </c>
     </row>
     <row r="101">
-      <c r="A101" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2202</t>
-        </is>
-      </c>
-      <c r="B101" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Art Directors</t>
-        </is>
-      </c>
-      <c r="C101" s="8"/>
-      <c r="D101" s="9">
-        <v>0</v>
-      </c>
-      <c r="E101" s="11"/>
-      <c r="F101" s="10">
-        <v>0</v>
-      </c>
-      <c r="G101" s="10">
-        <f>ROUND(D101*F101,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A101" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000 - Studios, Offices &amp; Workshops</t>
+        </is>
+      </c>
+      <c r="B101" s="7"/>
+      <c r="C101" s="7"/>
+      <c r="D101" s="7"/>
+      <c r="E101" s="7"/>
+      <c r="F101" s="7"/>
+      <c r="G101" s="7"/>
     </row>
     <row r="102">
       <c r="A102" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2203</t>
+          <t xml:space="preserve">1003</t>
         </is>
       </c>
       <c r="B102" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art Department Coordinator</t>
+          <t xml:space="preserve">Studio hire</t>
         </is>
       </c>
       <c r="C102" s="8"/>
@@ -2356,12 +2334,12 @@
     <row r="103">
       <c r="A103" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2204</t>
+          <t xml:space="preserve">1006</t>
         </is>
       </c>
       <c r="B103" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Draughtspersons</t>
+          <t xml:space="preserve">Production office hire</t>
         </is>
       </c>
       <c r="C103" s="8"/>
@@ -2380,12 +2358,12 @@
     <row r="104">
       <c r="A104" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2205</t>
+          <t xml:space="preserve">1009</t>
         </is>
       </c>
       <c r="B104" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clearance Coordinator</t>
+          <t xml:space="preserve">Workshop hire</t>
         </is>
       </c>
       <c r="C104" s="8"/>
@@ -2404,12 +2382,12 @@
     <row r="105">
       <c r="A105" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2211</t>
+          <t xml:space="preserve">1012</t>
         </is>
       </c>
       <c r="B105" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graphics Designer</t>
+          <t xml:space="preserve">Storage hire</t>
         </is>
       </c>
       <c r="C105" s="8"/>
@@ -2428,12 +2406,12 @@
     <row r="106">
       <c r="A106" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2212</t>
+          <t xml:space="preserve">1015</t>
         </is>
       </c>
       <c r="B106" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Story Board Artist</t>
+          <t xml:space="preserve">Utilities and cleaning</t>
         </is>
       </c>
       <c r="C106" s="8"/>
@@ -2452,12 +2430,12 @@
     <row r="107">
       <c r="A107" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213</t>
+          <t xml:space="preserve">1018</t>
         </is>
       </c>
       <c r="B107" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Concept Artist</t>
+          <t xml:space="preserve">Office furniture and equipment</t>
         </is>
       </c>
       <c r="C107" s="8"/>
@@ -2476,12 +2454,12 @@
     <row r="108">
       <c r="A108" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214</t>
+          <t xml:space="preserve">1021</t>
         </is>
       </c>
       <c r="B108" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Art Department Offices</t>
+          <t xml:space="preserve">Temporary internet and phones</t>
         </is>
       </c>
       <c r="C108" s="8"/>
@@ -2498,38 +2476,27 @@
       </c>
     </row>
     <row r="109">
-      <c r="A109" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2216</t>
-        </is>
-      </c>
-      <c r="B109" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Purchases &amp; Research Materials</t>
-        </is>
-      </c>
-      <c r="C109" s="8"/>
-      <c r="D109" s="9">
-        <v>0</v>
-      </c>
-      <c r="E109" s="11"/>
-      <c r="F109" s="10">
-        <v>0</v>
-      </c>
-      <c r="G109" s="10">
-        <f>ROUND(D109*F109,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A109" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1100 - Art Direction &amp; Design</t>
+        </is>
+      </c>
+      <c r="B109" s="7"/>
+      <c r="C109" s="7"/>
+      <c r="D109" s="7"/>
+      <c r="E109" s="7"/>
+      <c r="F109" s="7"/>
+      <c r="G109" s="7"/>
     </row>
     <row r="110">
       <c r="A110" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2217</t>
+          <t xml:space="preserve">1103</t>
         </is>
       </c>
       <c r="B110" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Production designer</t>
         </is>
       </c>
       <c r="C110" s="8"/>
@@ -2548,12 +2515,12 @@
     <row r="111">
       <c r="A111" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2285</t>
+          <t xml:space="preserve">1106</t>
         </is>
       </c>
       <c r="B111" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Costs</t>
+          <t xml:space="preserve">Supervising art director</t>
         </is>
       </c>
       <c r="C111" s="8"/>
@@ -2570,27 +2537,38 @@
       </c>
     </row>
     <row r="112">
-      <c r="A112" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2300 - Construction</t>
-        </is>
-      </c>
-      <c r="B112" s="7"/>
-      <c r="C112" s="7"/>
-      <c r="D112" s="7"/>
-      <c r="E112" s="7"/>
-      <c r="F112" s="7"/>
-      <c r="G112" s="7"/>
+      <c r="A112" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1109</t>
+        </is>
+      </c>
+      <c r="B112" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Art director</t>
+        </is>
+      </c>
+      <c r="C112" s="8"/>
+      <c r="D112" s="9">
+        <v>0</v>
+      </c>
+      <c r="E112" s="11"/>
+      <c r="F112" s="10">
+        <v>0</v>
+      </c>
+      <c r="G112" s="10">
+        <f>ROUND(D112*F112,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301</t>
+          <t xml:space="preserve">1112</t>
         </is>
       </c>
       <c r="B113" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction Manager</t>
+          <t xml:space="preserve">Art department coordinator</t>
         </is>
       </c>
       <c r="C113" s="8"/>
@@ -2609,12 +2587,12 @@
     <row r="114">
       <c r="A114" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2302</t>
+          <t xml:space="preserve">1115</t>
         </is>
       </c>
       <c r="B114" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction Foreman</t>
+          <t xml:space="preserve">Set designer and draughting</t>
         </is>
       </c>
       <c r="C114" s="8"/>
@@ -2633,12 +2611,12 @@
     <row r="115">
       <c r="A115" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2303</t>
+          <t xml:space="preserve">1118</t>
         </is>
       </c>
       <c r="B115" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fabrications</t>
+          <t xml:space="preserve">Concept artist</t>
         </is>
       </c>
       <c r="C115" s="8"/>
@@ -2657,12 +2635,12 @@
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2304</t>
+          <t xml:space="preserve">1121</t>
         </is>
       </c>
       <c r="B116" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greens</t>
+          <t xml:space="preserve">Graphic designer</t>
         </is>
       </c>
       <c r="C116" s="8"/>
@@ -2681,12 +2659,12 @@
     <row r="117">
       <c r="A117" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2305</t>
+          <t xml:space="preserve">1124</t>
         </is>
       </c>
       <c r="B117" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scenics</t>
+          <t xml:space="preserve">Art department assistants</t>
         </is>
       </c>
       <c r="C117" s="8"/>
@@ -2705,12 +2683,12 @@
     <row r="118">
       <c r="A118" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306</t>
+          <t xml:space="preserve">1127</t>
         </is>
       </c>
       <c r="B118" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steel</t>
+          <t xml:space="preserve">Art research and reference</t>
         </is>
       </c>
       <c r="C118" s="8"/>
@@ -2727,38 +2705,27 @@
       </c>
     </row>
     <row r="119">
-      <c r="A119" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2307</t>
-        </is>
-      </c>
-      <c r="B119" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Riggers</t>
-        </is>
-      </c>
-      <c r="C119" s="8"/>
-      <c r="D119" s="9">
-        <v>0</v>
-      </c>
-      <c r="E119" s="11"/>
-      <c r="F119" s="10">
-        <v>0</v>
-      </c>
-      <c r="G119" s="10">
-        <f>ROUND(D119*F119,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A119" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1200 - Construction, Scenic &amp; Greens</t>
+        </is>
+      </c>
+      <c r="B119" s="7"/>
+      <c r="C119" s="7"/>
+      <c r="D119" s="7"/>
+      <c r="E119" s="7"/>
+      <c r="F119" s="7"/>
+      <c r="G119" s="7"/>
     </row>
     <row r="120">
       <c r="A120" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2308</t>
+          <t xml:space="preserve">1203</t>
         </is>
       </c>
       <c r="B120" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction Admin</t>
+          <t xml:space="preserve">Construction manager</t>
         </is>
       </c>
       <c r="C120" s="8"/>
@@ -2777,12 +2744,12 @@
     <row r="121">
       <c r="A121" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309</t>
+          <t xml:space="preserve">1206</t>
         </is>
       </c>
       <c r="B121" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stagehands</t>
+          <t xml:space="preserve">Construction crew</t>
         </is>
       </c>
       <c r="C121" s="8"/>
@@ -2801,12 +2768,12 @@
     <row r="122">
       <c r="A122" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2318</t>
+          <t xml:space="preserve">1209</t>
         </is>
       </c>
       <c r="B122" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Addt'l Labor</t>
+          <t xml:space="preserve">Carpentry and fabrication</t>
         </is>
       </c>
       <c r="C122" s="8"/>
@@ -2825,12 +2792,12 @@
     <row r="123">
       <c r="A123" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319</t>
+          <t xml:space="preserve">1212</t>
         </is>
       </c>
       <c r="B123" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction Medic</t>
+          <t xml:space="preserve">Metalwork and rigging labour</t>
         </is>
       </c>
       <c r="C123" s="8"/>
@@ -2849,12 +2816,12 @@
     <row r="124">
       <c r="A124" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2330</t>
+          <t xml:space="preserve">1215</t>
         </is>
       </c>
       <c r="B124" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outside Contracts</t>
+          <t xml:space="preserve">Scenic artists</t>
         </is>
       </c>
       <c r="C124" s="8"/>
@@ -2873,12 +2840,12 @@
     <row r="125">
       <c r="A125" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2332</t>
+          <t xml:space="preserve">1218</t>
         </is>
       </c>
       <c r="B125" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Outside Manufacturing</t>
+          <t xml:space="preserve">Paint and scenic materials</t>
         </is>
       </c>
       <c r="C125" s="8"/>
@@ -2897,12 +2864,12 @@
     <row r="126">
       <c r="A126" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2334</t>
+          <t xml:space="preserve">1221</t>
         </is>
       </c>
       <c r="B126" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Construction Materials</t>
+          <t xml:space="preserve">Greens crew and materials</t>
         </is>
       </c>
       <c r="C126" s="8"/>
@@ -2921,12 +2888,12 @@
     <row r="127">
       <c r="A127" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2351</t>
+          <t xml:space="preserve">1224</t>
         </is>
       </c>
       <c r="B127" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Paint Materials</t>
+          <t xml:space="preserve">Construction plant and tools</t>
         </is>
       </c>
       <c r="C127" s="8"/>
@@ -2945,12 +2912,12 @@
     <row r="128">
       <c r="A128" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2352</t>
+          <t xml:space="preserve">1227</t>
         </is>
       </c>
       <c r="B128" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greens Materials</t>
+          <t xml:space="preserve">Scaffolding and access equipment</t>
         </is>
       </c>
       <c r="C128" s="8"/>
@@ -2969,12 +2936,12 @@
     <row r="129">
       <c r="A129" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2359</t>
+          <t xml:space="preserve">1230</t>
         </is>
       </c>
       <c r="B129" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Labour &amp; Materials</t>
+          <t xml:space="preserve">Strike and waste removal</t>
         </is>
       </c>
       <c r="C129" s="8"/>
@@ -2991,38 +2958,27 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2370</t>
-        </is>
-      </c>
-      <c r="B130" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rentals</t>
-        </is>
-      </c>
-      <c r="C130" s="8"/>
-      <c r="D130" s="9">
-        <v>0</v>
-      </c>
-      <c r="E130" s="11"/>
-      <c r="F130" s="10">
-        <v>0</v>
-      </c>
-      <c r="G130" s="10">
-        <f>ROUND(D130*F130,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A130" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1300 - Set Decoration, Props &amp; Graphics</t>
+        </is>
+      </c>
+      <c r="B130" s="7"/>
+      <c r="C130" s="7"/>
+      <c r="D130" s="7"/>
+      <c r="E130" s="7"/>
+      <c r="F130" s="7"/>
+      <c r="G130" s="7"/>
     </row>
     <row r="131">
       <c r="A131" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2372</t>
+          <t xml:space="preserve">1303</t>
         </is>
       </c>
       <c r="B131" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health &amp; Safety</t>
+          <t xml:space="preserve">Set decorator</t>
         </is>
       </c>
       <c r="C131" s="8"/>
@@ -3041,12 +2997,12 @@
     <row r="132">
       <c r="A132" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2374</t>
+          <t xml:space="preserve">1306</t>
         </is>
       </c>
       <c r="B132" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Backings/Translights</t>
+          <t xml:space="preserve">Set decoration crew</t>
         </is>
       </c>
       <c r="C132" s="8"/>
@@ -3065,12 +3021,12 @@
     <row r="133">
       <c r="A133" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376</t>
+          <t xml:space="preserve">1309</t>
         </is>
       </c>
       <c r="B133" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scaffolding</t>
+          <t xml:space="preserve">Set dressing purchases</t>
         </is>
       </c>
       <c r="C133" s="8"/>
@@ -3089,12 +3045,12 @@
     <row r="134">
       <c r="A134" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2378</t>
+          <t xml:space="preserve">1312</t>
         </is>
       </c>
       <c r="B134" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Set dressing rentals</t>
         </is>
       </c>
       <c r="C134" s="8"/>
@@ -3113,12 +3069,12 @@
     <row r="135">
       <c r="A135" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2380</t>
+          <t xml:space="preserve">1315</t>
         </is>
       </c>
       <c r="B135" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Property master</t>
         </is>
       </c>
       <c r="C135" s="8"/>
@@ -3135,27 +3091,38 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2400 - Set Dressing</t>
-        </is>
-      </c>
-      <c r="B136" s="7"/>
-      <c r="C136" s="7"/>
-      <c r="D136" s="7"/>
-      <c r="E136" s="7"/>
-      <c r="F136" s="7"/>
-      <c r="G136" s="7"/>
+      <c r="A136" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1318</t>
+        </is>
+      </c>
+      <c r="B136" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Standby props</t>
+        </is>
+      </c>
+      <c r="C136" s="8"/>
+      <c r="D136" s="9">
+        <v>0</v>
+      </c>
+      <c r="E136" s="11"/>
+      <c r="F136" s="10">
+        <v>0</v>
+      </c>
+      <c r="G136" s="10">
+        <f>ROUND(D136*F136,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2401</t>
+          <t xml:space="preserve">1321</t>
         </is>
       </c>
       <c r="B137" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set Decorator</t>
+          <t xml:space="preserve">Props manufacture</t>
         </is>
       </c>
       <c r="C137" s="8"/>
@@ -3174,12 +3141,12 @@
     <row r="138">
       <c r="A138" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2402</t>
+          <t xml:space="preserve">1324</t>
         </is>
       </c>
       <c r="B138" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Leadman</t>
+          <t xml:space="preserve">Props purchases and rentals</t>
         </is>
       </c>
       <c r="C138" s="8"/>
@@ -3198,12 +3165,12 @@
     <row r="139">
       <c r="A139" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403</t>
+          <t xml:space="preserve">1327</t>
         </is>
       </c>
       <c r="B139" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swing Gang</t>
+          <t xml:space="preserve">On-set graphics</t>
         </is>
       </c>
       <c r="C139" s="8"/>
@@ -3222,12 +3189,12 @@
     <row r="140">
       <c r="A140" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2404</t>
+          <t xml:space="preserve">1330</t>
         </is>
       </c>
       <c r="B140" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Swing Gang Dailies</t>
+          <t xml:space="preserve">Weapons and armoury</t>
         </is>
       </c>
       <c r="C140" s="8"/>
@@ -3246,12 +3213,12 @@
     <row r="141">
       <c r="A141" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2405</t>
+          <t xml:space="preserve">1333</t>
         </is>
       </c>
       <c r="B141" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set Dressers</t>
+          <t xml:space="preserve">Loss and damage allowance</t>
         </is>
       </c>
       <c r="C141" s="8"/>
@@ -3268,38 +3235,27 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2406</t>
-        </is>
-      </c>
-      <c r="B142" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Purchases &amp; Rentals</t>
-        </is>
-      </c>
-      <c r="C142" s="8"/>
-      <c r="D142" s="9">
-        <v>0</v>
-      </c>
-      <c r="E142" s="11"/>
-      <c r="F142" s="10">
-        <v>0</v>
-      </c>
-      <c r="G142" s="10">
-        <f>ROUND(D142*F142,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A142" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1400 - Costume &amp; Wardrobe</t>
+        </is>
+      </c>
+      <c r="B142" s="7"/>
+      <c r="C142" s="7"/>
+      <c r="D142" s="7"/>
+      <c r="E142" s="7"/>
+      <c r="F142" s="7"/>
+      <c r="G142" s="7"/>
     </row>
     <row r="143">
       <c r="A143" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2411</t>
+          <t xml:space="preserve">1403</t>
         </is>
       </c>
       <c r="B143" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Graphics</t>
+          <t xml:space="preserve">Costume designer</t>
         </is>
       </c>
       <c r="C143" s="8"/>
@@ -3318,12 +3274,12 @@
     <row r="144">
       <c r="A144" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2414</t>
+          <t xml:space="preserve">1406</t>
         </is>
       </c>
       <c r="B144" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Greens Labour &amp; Materials</t>
+          <t xml:space="preserve">Costume supervisor</t>
         </is>
       </c>
       <c r="C144" s="8"/>
@@ -3342,12 +3298,12 @@
     <row r="145">
       <c r="A145" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2446</t>
+          <t xml:space="preserve">1409</t>
         </is>
       </c>
       <c r="B145" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Set Dec Store Rental</t>
+          <t xml:space="preserve">Costume buyers</t>
         </is>
       </c>
       <c r="C145" s="8"/>
@@ -3366,12 +3322,12 @@
     <row r="146">
       <c r="A146" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2450</t>
+          <t xml:space="preserve">1412</t>
         </is>
       </c>
       <c r="B146" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Wardrobe assistants</t>
         </is>
       </c>
       <c r="C146" s="8"/>
@@ -3390,12 +3346,12 @@
     <row r="147">
       <c r="A147" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2498</t>
+          <t xml:space="preserve">1415</t>
         </is>
       </c>
       <c r="B147" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Standby wardrobe</t>
         </is>
       </c>
       <c r="C147" s="8"/>
@@ -3412,27 +3368,38 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2500 - Property</t>
-        </is>
-      </c>
-      <c r="B148" s="7"/>
-      <c r="C148" s="7"/>
-      <c r="D148" s="7"/>
-      <c r="E148" s="7"/>
-      <c r="F148" s="7"/>
-      <c r="G148" s="7"/>
+      <c r="A148" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1418</t>
+        </is>
+      </c>
+      <c r="B148" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Costume making and alterations</t>
+        </is>
+      </c>
+      <c r="C148" s="8"/>
+      <c r="D148" s="9">
+        <v>0</v>
+      </c>
+      <c r="E148" s="11"/>
+      <c r="F148" s="10">
+        <v>0</v>
+      </c>
+      <c r="G148" s="10">
+        <f>ROUND(D148*F148,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2501</t>
+          <t xml:space="preserve">1421</t>
         </is>
       </c>
       <c r="B149" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Property Master</t>
+          <t xml:space="preserve">Costume purchases</t>
         </is>
       </c>
       <c r="C149" s="8"/>
@@ -3451,12 +3418,12 @@
     <row r="150">
       <c r="A150" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2502</t>
+          <t xml:space="preserve">1424</t>
         </is>
       </c>
       <c r="B150" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asst Propmaster</t>
+          <t xml:space="preserve">Costume rentals</t>
         </is>
       </c>
       <c r="C150" s="8"/>
@@ -3475,12 +3442,12 @@
     <row r="151">
       <c r="A151" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503</t>
+          <t xml:space="preserve">1427</t>
         </is>
       </c>
       <c r="B151" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standby Props</t>
+          <t xml:space="preserve">Laundry and dry cleaning</t>
         </is>
       </c>
       <c r="C151" s="8"/>
@@ -3499,12 +3466,12 @@
     <row r="152">
       <c r="A152" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2504</t>
+          <t xml:space="preserve">1430</t>
         </is>
       </c>
       <c r="B152" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additional Labour</t>
+          <t xml:space="preserve">Wardrobe workspace and supplies</t>
         </is>
       </c>
       <c r="C152" s="8"/>
@@ -3521,38 +3488,27 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2505</t>
-        </is>
-      </c>
-      <c r="B153" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Purchases</t>
-        </is>
-      </c>
-      <c r="C153" s="8"/>
-      <c r="D153" s="9">
-        <v>0</v>
-      </c>
-      <c r="E153" s="11"/>
-      <c r="F153" s="10">
-        <v>0</v>
-      </c>
-      <c r="G153" s="10">
-        <f>ROUND(D153*F153,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A153" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1500 - Hair, Makeup &amp; Prosthetics</t>
+        </is>
+      </c>
+      <c r="B153" s="7"/>
+      <c r="C153" s="7"/>
+      <c r="D153" s="7"/>
+      <c r="E153" s="7"/>
+      <c r="F153" s="7"/>
+      <c r="G153" s="7"/>
     </row>
     <row r="154">
       <c r="A154" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2506</t>
+          <t xml:space="preserve">1503</t>
         </is>
       </c>
       <c r="B154" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rentals &amp; Manufacturing</t>
+          <t xml:space="preserve">Hair and makeup designer</t>
         </is>
       </c>
       <c r="C154" s="8"/>
@@ -3571,12 +3527,12 @@
     <row r="155">
       <c r="A155" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2520</t>
+          <t xml:space="preserve">1506</t>
         </is>
       </c>
       <c r="B155" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Armoury &amp; Weapons</t>
+          <t xml:space="preserve">Hair artists</t>
         </is>
       </c>
       <c r="C155" s="8"/>
@@ -3595,12 +3551,12 @@
     <row r="156">
       <c r="A156" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2530</t>
+          <t xml:space="preserve">1509</t>
         </is>
       </c>
       <c r="B156" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Makeup artists</t>
         </is>
       </c>
       <c r="C156" s="8"/>
@@ -3619,12 +3575,12 @@
     <row r="157">
       <c r="A157" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2598</t>
+          <t xml:space="preserve">1512</t>
         </is>
       </c>
       <c r="B157" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Additional daily crew</t>
         </is>
       </c>
       <c r="C157" s="8"/>
@@ -3641,27 +3597,38 @@
       </c>
     </row>
     <row r="158">
-      <c r="A158" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2600 - Picture Vehicles &amp; Animals</t>
-        </is>
-      </c>
-      <c r="B158" s="7"/>
-      <c r="C158" s="7"/>
-      <c r="D158" s="7"/>
-      <c r="E158" s="7"/>
-      <c r="F158" s="7"/>
-      <c r="G158" s="7"/>
+      <c r="A158" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1515</t>
+        </is>
+      </c>
+      <c r="B158" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Prosthetic design and application</t>
+        </is>
+      </c>
+      <c r="C158" s="8"/>
+      <c r="D158" s="9">
+        <v>0</v>
+      </c>
+      <c r="E158" s="11"/>
+      <c r="F158" s="10">
+        <v>0</v>
+      </c>
+      <c r="G158" s="10">
+        <f>ROUND(D158*F158,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2601</t>
+          <t xml:space="preserve">1518</t>
         </is>
       </c>
       <c r="B159" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Picture Car Co-Ordinator</t>
+          <t xml:space="preserve">Wigs and hairpieces</t>
         </is>
       </c>
       <c r="C159" s="8"/>
@@ -3680,12 +3647,12 @@
     <row r="160">
       <c r="A160" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2602</t>
+          <t xml:space="preserve">1521</t>
         </is>
       </c>
       <c r="B160" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mechanic</t>
+          <t xml:space="preserve">Makeup consumables</t>
         </is>
       </c>
       <c r="C160" s="8"/>
@@ -3704,12 +3671,12 @@
     <row r="161">
       <c r="A161" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2605</t>
+          <t xml:space="preserve">1524</t>
         </is>
       </c>
       <c r="B161" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Action Vehicles</t>
+          <t xml:space="preserve">Hair and makeup facilities</t>
         </is>
       </c>
       <c r="C161" s="8"/>
@@ -3726,38 +3693,27 @@
       </c>
     </row>
     <row r="162">
-      <c r="A162" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2606</t>
-        </is>
-      </c>
-      <c r="B162" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Transportation</t>
-        </is>
-      </c>
-      <c r="C162" s="8"/>
-      <c r="D162" s="9">
-        <v>0</v>
-      </c>
-      <c r="E162" s="11"/>
-      <c r="F162" s="10">
-        <v>0</v>
-      </c>
-      <c r="G162" s="10">
-        <f>ROUND(D162*F162,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A162" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1600 - Camera &amp; Imaging</t>
+        </is>
+      </c>
+      <c r="B162" s="7"/>
+      <c r="C162" s="7"/>
+      <c r="D162" s="7"/>
+      <c r="E162" s="7"/>
+      <c r="F162" s="7"/>
+      <c r="G162" s="7"/>
     </row>
     <row r="163">
       <c r="A163" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2609</t>
+          <t xml:space="preserve">1603</t>
         </is>
       </c>
       <c r="B163" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repairs/Modifications</t>
+          <t xml:space="preserve">Director of photography</t>
         </is>
       </c>
       <c r="C163" s="8"/>
@@ -3776,12 +3732,12 @@
     <row r="164">
       <c r="A164" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2610</t>
+          <t xml:space="preserve">1606</t>
         </is>
       </c>
       <c r="B164" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Animals &amp; Animal Wranglers</t>
+          <t xml:space="preserve">Camera operators</t>
         </is>
       </c>
       <c r="C164" s="8"/>
@@ -3800,12 +3756,12 @@
     <row r="165">
       <c r="A165" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2611</t>
+          <t xml:space="preserve">1609</t>
         </is>
       </c>
       <c r="B165" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Animal Welfare</t>
+          <t xml:space="preserve">First camera assistants</t>
         </is>
       </c>
       <c r="C165" s="8"/>
@@ -3824,12 +3780,12 @@
     <row r="166">
       <c r="A166" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2612</t>
+          <t xml:space="preserve">1612</t>
         </is>
       </c>
       <c r="B166" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Permits</t>
+          <t xml:space="preserve">Second camera assistants</t>
         </is>
       </c>
       <c r="C166" s="8"/>
@@ -3848,12 +3804,12 @@
     <row r="167">
       <c r="A167" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2613</t>
+          <t xml:space="preserve">1615</t>
         </is>
       </c>
       <c r="B167" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Animal Travel And Living</t>
+          <t xml:space="preserve">Camera trainees</t>
         </is>
       </c>
       <c r="C167" s="8"/>
@@ -3872,12 +3828,12 @@
     <row r="168">
       <c r="A168" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2620</t>
+          <t xml:space="preserve">1618</t>
         </is>
       </c>
       <c r="B168" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Digital imaging technician</t>
         </is>
       </c>
       <c r="C168" s="8"/>
@@ -3894,27 +3850,38 @@
       </c>
     </row>
     <row r="169">
-      <c r="A169" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2700 - Special Effects</t>
-        </is>
-      </c>
-      <c r="B169" s="7"/>
-      <c r="C169" s="7"/>
-      <c r="D169" s="7"/>
-      <c r="E169" s="7"/>
-      <c r="F169" s="7"/>
-      <c r="G169" s="7"/>
+      <c r="A169" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1621</t>
+        </is>
+      </c>
+      <c r="B169" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Camera equipment package</t>
+        </is>
+      </c>
+      <c r="C169" s="8"/>
+      <c r="D169" s="9">
+        <v>0</v>
+      </c>
+      <c r="E169" s="11"/>
+      <c r="F169" s="10">
+        <v>0</v>
+      </c>
+      <c r="G169" s="10">
+        <f>ROUND(D169*F169,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2701</t>
+          <t xml:space="preserve">1624</t>
         </is>
       </c>
       <c r="B170" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFX Supervisor</t>
+          <t xml:space="preserve">Lenses and specialist optics</t>
         </is>
       </c>
       <c r="C170" s="8"/>
@@ -3933,12 +3900,12 @@
     <row r="171">
       <c r="A171" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2702</t>
+          <t xml:space="preserve">1627</t>
         </is>
       </c>
       <c r="B171" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFX Floor Supervisor</t>
+          <t xml:space="preserve">Remote heads and stabilisers</t>
         </is>
       </c>
       <c r="C171" s="8"/>
@@ -3957,12 +3924,12 @@
     <row r="172">
       <c r="A172" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2703</t>
+          <t xml:space="preserve">1630</t>
         </is>
       </c>
       <c r="B172" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFX Foreman</t>
+          <t xml:space="preserve">Aerial and drone camera</t>
         </is>
       </c>
       <c r="C172" s="8"/>
@@ -3981,12 +3948,12 @@
     <row r="173">
       <c r="A173" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2704</t>
+          <t xml:space="preserve">1633</t>
         </is>
       </c>
       <c r="B173" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">SFX Technicians</t>
+          <t xml:space="preserve">Underwater camera</t>
         </is>
       </c>
       <c r="C173" s="8"/>
@@ -4005,12 +3972,12 @@
     <row r="174">
       <c r="A174" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2705</t>
+          <t xml:space="preserve">1636</t>
         </is>
       </c>
       <c r="B174" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workshop Crew</t>
+          <t xml:space="preserve">Unit stills photography</t>
         </is>
       </c>
       <c r="C174" s="8"/>
@@ -4029,12 +3996,12 @@
     <row r="175">
       <c r="A175" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2706</t>
+          <t xml:space="preserve">1639</t>
         </is>
       </c>
       <c r="B175" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workshop Rentals</t>
+          <t xml:space="preserve">Camera consumables</t>
         </is>
       </c>
       <c r="C175" s="8"/>
@@ -4053,12 +4020,12 @@
     <row r="176">
       <c r="A176" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2707</t>
+          <t xml:space="preserve">1642</t>
         </is>
       </c>
       <c r="B176" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prosthetics</t>
+          <t xml:space="preserve">Camera loss and damage allowance</t>
         </is>
       </c>
       <c r="C176" s="8"/>
@@ -4075,51 +4042,51 @@
       </c>
     </row>
     <row r="177">
-      <c r="A177" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2716</t>
-        </is>
-      </c>
-      <c r="B177" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rentals &amp; Purchases</t>
-        </is>
-      </c>
-      <c r="C177" s="8"/>
-      <c r="D177" s="9">
-        <v>0</v>
-      </c>
-      <c r="E177" s="11"/>
-      <c r="F177" s="10">
-        <v>0</v>
-      </c>
-      <c r="G177" s="10">
-        <f>ROUND(D177*F177,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A177" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1700 - Lighting &amp; Electrical</t>
+        </is>
+      </c>
+      <c r="B177" s="7"/>
+      <c r="C177" s="7"/>
+      <c r="D177" s="7"/>
+      <c r="E177" s="7"/>
+      <c r="F177" s="7"/>
+      <c r="G177" s="7"/>
     </row>
     <row r="178">
-      <c r="A178" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2800 - Tests</t>
-        </is>
-      </c>
-      <c r="B178" s="7"/>
-      <c r="C178" s="7"/>
-      <c r="D178" s="7"/>
-      <c r="E178" s="7"/>
-      <c r="F178" s="7"/>
-      <c r="G178" s="7"/>
+      <c r="A178" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1703</t>
+        </is>
+      </c>
+      <c r="B178" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Gaffer</t>
+        </is>
+      </c>
+      <c r="C178" s="8"/>
+      <c r="D178" s="9">
+        <v>0</v>
+      </c>
+      <c r="E178" s="11"/>
+      <c r="F178" s="10">
+        <v>0</v>
+      </c>
+      <c r="G178" s="10">
+        <f>ROUND(D178*F178,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2801</t>
+          <t xml:space="preserve">1706</t>
         </is>
       </c>
       <c r="B179" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Tests</t>
+          <t xml:space="preserve">Lighting console operator</t>
         </is>
       </c>
       <c r="C179" s="8"/>
@@ -4136,27 +4103,38 @@
       </c>
     </row>
     <row r="180">
-      <c r="A180" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2900 - Stages, Offices &amp; Workshops</t>
-        </is>
-      </c>
-      <c r="B180" s="7"/>
-      <c r="C180" s="7"/>
-      <c r="D180" s="7"/>
-      <c r="E180" s="7"/>
-      <c r="F180" s="7"/>
-      <c r="G180" s="7"/>
+      <c r="A180" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1709</t>
+        </is>
+      </c>
+      <c r="B180" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lighting technicians</t>
+        </is>
+      </c>
+      <c r="C180" s="8"/>
+      <c r="D180" s="9">
+        <v>0</v>
+      </c>
+      <c r="E180" s="11"/>
+      <c r="F180" s="10">
+        <v>0</v>
+      </c>
+      <c r="G180" s="10">
+        <f>ROUND(D180*F180,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="181">
       <c r="A181" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2901</t>
+          <t xml:space="preserve">1712</t>
         </is>
       </c>
       <c r="B181" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stage Hire</t>
+          <t xml:space="preserve">Rigging electricians</t>
         </is>
       </c>
       <c r="C181" s="8"/>
@@ -4175,12 +4153,12 @@
     <row r="182">
       <c r="A182" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2905</t>
+          <t xml:space="preserve">1715</t>
         </is>
       </c>
       <c r="B182" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Office Hire</t>
+          <t xml:space="preserve">Generator operator</t>
         </is>
       </c>
       <c r="C182" s="8"/>
@@ -4199,12 +4177,12 @@
     <row r="183">
       <c r="A183" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2910</t>
+          <t xml:space="preserve">1718</t>
         </is>
       </c>
       <c r="B183" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Storerooms</t>
+          <t xml:space="preserve">Lighting equipment package</t>
         </is>
       </c>
       <c r="C183" s="8"/>
@@ -4223,12 +4201,12 @@
     <row r="184">
       <c r="A184" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">2915</t>
+          <t xml:space="preserve">1721</t>
         </is>
       </c>
       <c r="B184" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Workshops</t>
+          <t xml:space="preserve">Generators and power distribution</t>
         </is>
       </c>
       <c r="C184" s="8"/>
@@ -4245,27 +4223,38 @@
       </c>
     </row>
     <row r="185">
-      <c r="A185" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3000 - Camera</t>
-        </is>
-      </c>
-      <c r="B185" s="7"/>
-      <c r="C185" s="7"/>
-      <c r="D185" s="7"/>
-      <c r="E185" s="7"/>
-      <c r="F185" s="7"/>
-      <c r="G185" s="7"/>
+      <c r="A185" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1724</t>
+        </is>
+      </c>
+      <c r="B185" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Practical lighting</t>
+        </is>
+      </c>
+      <c r="C185" s="8"/>
+      <c r="D185" s="9">
+        <v>0</v>
+      </c>
+      <c r="E185" s="11"/>
+      <c r="F185" s="10">
+        <v>0</v>
+      </c>
+      <c r="G185" s="10">
+        <f>ROUND(D185*F185,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="186">
       <c r="A186" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3001</t>
+          <t xml:space="preserve">1727</t>
         </is>
       </c>
       <c r="B186" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Director Of Photography</t>
+          <t xml:space="preserve">Lighting consumables</t>
         </is>
       </c>
       <c r="C186" s="8"/>
@@ -4284,12 +4273,12 @@
     <row r="187">
       <c r="A187" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3002</t>
+          <t xml:space="preserve">1730</t>
         </is>
       </c>
       <c r="B187" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camera Operators</t>
+          <t xml:space="preserve">Electrical loss and damage allowance</t>
         </is>
       </c>
       <c r="C187" s="8"/>
@@ -4306,38 +4295,27 @@
       </c>
     </row>
     <row r="188">
-      <c r="A188" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3004</t>
-        </is>
-      </c>
-      <c r="B188" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Steadicam Operators</t>
-        </is>
-      </c>
-      <c r="C188" s="8"/>
-      <c r="D188" s="9">
-        <v>0</v>
-      </c>
-      <c r="E188" s="11"/>
-      <c r="F188" s="10">
-        <v>0</v>
-      </c>
-      <c r="G188" s="10">
-        <f>ROUND(D188*F188,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A188" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1800 - Grip, Rigging &amp; Camera Movement</t>
+        </is>
+      </c>
+      <c r="B188" s="7"/>
+      <c r="C188" s="7"/>
+      <c r="D188" s="7"/>
+      <c r="E188" s="7"/>
+      <c r="F188" s="7"/>
+      <c r="G188" s="7"/>
     </row>
     <row r="189">
       <c r="A189" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3005</t>
+          <t xml:space="preserve">1803</t>
         </is>
       </c>
       <c r="B189" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Focus Pullers</t>
+          <t xml:space="preserve">Key grip</t>
         </is>
       </c>
       <c r="C189" s="8"/>
@@ -4356,12 +4334,12 @@
     <row r="190">
       <c r="A190" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3006</t>
+          <t xml:space="preserve">1806</t>
         </is>
       </c>
       <c r="B190" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Clapper/Loaders</t>
+          <t xml:space="preserve">Grip team</t>
         </is>
       </c>
       <c r="C190" s="8"/>
@@ -4380,12 +4358,12 @@
     <row r="191">
       <c r="A191" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3007</t>
+          <t xml:space="preserve">1809</t>
         </is>
       </c>
       <c r="B191" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camera Assistant/Trainee</t>
+          <t xml:space="preserve">Rigging grips</t>
         </is>
       </c>
       <c r="C191" s="8"/>
@@ -4404,12 +4382,12 @@
     <row r="192">
       <c r="A192" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3008</t>
+          <t xml:space="preserve">1812</t>
         </is>
       </c>
       <c r="B192" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">DIT</t>
+          <t xml:space="preserve">Dolly grip</t>
         </is>
       </c>
       <c r="C192" s="8"/>
@@ -4428,12 +4406,12 @@
     <row r="193">
       <c r="A193" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3016</t>
+          <t xml:space="preserve">1815</t>
         </is>
       </c>
       <c r="B193" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camera Purchases</t>
+          <t xml:space="preserve">Grip equipment package</t>
         </is>
       </c>
       <c r="C193" s="8"/>
@@ -4452,12 +4430,12 @@
     <row r="194">
       <c r="A194" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3018</t>
+          <t xml:space="preserve">1818</t>
         </is>
       </c>
       <c r="B194" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Camera Package Rental</t>
+          <t xml:space="preserve">Dollies and track</t>
         </is>
       </c>
       <c r="C194" s="8"/>
@@ -4476,12 +4454,12 @@
     <row r="195">
       <c r="A195" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3019</t>
+          <t xml:space="preserve">1821</t>
         </is>
       </c>
       <c r="B195" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Steadicam</t>
+          <t xml:space="preserve">Cranes and jibs</t>
         </is>
       </c>
       <c r="C195" s="8"/>
@@ -4500,12 +4478,12 @@
     <row r="196">
       <c r="A196" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3020</t>
+          <t xml:space="preserve">1824</t>
         </is>
       </c>
       <c r="B196" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Still Photographer</t>
+          <t xml:space="preserve">Vehicle mounts</t>
         </is>
       </c>
       <c r="C196" s="8"/>
@@ -4524,12 +4502,12 @@
     <row r="197">
       <c r="A197" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3030</t>
+          <t xml:space="preserve">1827</t>
         </is>
       </c>
       <c r="B197" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Aerial Photography</t>
+          <t xml:space="preserve">Access and lifting equipment</t>
         </is>
       </c>
       <c r="C197" s="8"/>
@@ -4548,12 +4526,12 @@
     <row r="198">
       <c r="A198" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3040</t>
+          <t xml:space="preserve">1830</t>
         </is>
       </c>
       <c r="B198" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Underwater Photography</t>
+          <t xml:space="preserve">Rigging consumables</t>
         </is>
       </c>
       <c r="C198" s="8"/>
@@ -4572,12 +4550,12 @@
     <row r="199">
       <c r="A199" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3050</t>
+          <t xml:space="preserve">1833</t>
         </is>
       </c>
       <c r="B199" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rental</t>
+          <t xml:space="preserve">Grip loss and damage allowance</t>
         </is>
       </c>
       <c r="C199" s="8"/>
@@ -4594,51 +4572,51 @@
       </c>
     </row>
     <row r="200">
-      <c r="A200" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3098</t>
-        </is>
-      </c>
-      <c r="B200" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
-        </is>
-      </c>
-      <c r="C200" s="8"/>
-      <c r="D200" s="9">
-        <v>0</v>
-      </c>
-      <c r="E200" s="11"/>
-      <c r="F200" s="10">
-        <v>0</v>
-      </c>
-      <c r="G200" s="10">
-        <f>ROUND(D200*F200,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A200" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1900 - Production Sound &amp; Communications</t>
+        </is>
+      </c>
+      <c r="B200" s="7"/>
+      <c r="C200" s="7"/>
+      <c r="D200" s="7"/>
+      <c r="E200" s="7"/>
+      <c r="F200" s="7"/>
+      <c r="G200" s="7"/>
     </row>
     <row r="201">
-      <c r="A201" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3100 - Grips &amp; Set Operations</t>
-        </is>
-      </c>
-      <c r="B201" s="7"/>
-      <c r="C201" s="7"/>
-      <c r="D201" s="7"/>
-      <c r="E201" s="7"/>
-      <c r="F201" s="7"/>
-      <c r="G201" s="7"/>
+      <c r="A201" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1903</t>
+        </is>
+      </c>
+      <c r="B201" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Production sound mixer</t>
+        </is>
+      </c>
+      <c r="C201" s="8"/>
+      <c r="D201" s="9">
+        <v>0</v>
+      </c>
+      <c r="E201" s="11"/>
+      <c r="F201" s="10">
+        <v>0</v>
+      </c>
+      <c r="G201" s="10">
+        <f>ROUND(D201*F201,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="202">
       <c r="A202" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3101</t>
+          <t xml:space="preserve">1906</t>
         </is>
       </c>
       <c r="B202" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Key Grip</t>
+          <t xml:space="preserve">Boom operator</t>
         </is>
       </c>
       <c r="C202" s="8"/>
@@ -4657,12 +4635,12 @@
     <row r="203">
       <c r="A203" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3102</t>
+          <t xml:space="preserve">1909</t>
         </is>
       </c>
       <c r="B203" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best Boy Grip</t>
+          <t xml:space="preserve">Sound assistant</t>
         </is>
       </c>
       <c r="C203" s="8"/>
@@ -4681,12 +4659,12 @@
     <row r="204">
       <c r="A204" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3103</t>
+          <t xml:space="preserve">1912</t>
         </is>
       </c>
       <c r="B204" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dolly Grips</t>
+          <t xml:space="preserve">Production sound package</t>
         </is>
       </c>
       <c r="C204" s="8"/>
@@ -4705,12 +4683,12 @@
     <row r="205">
       <c r="A205" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3104</t>
+          <t xml:space="preserve">1915</t>
         </is>
       </c>
       <c r="B205" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Company Grips</t>
+          <t xml:space="preserve">Radio microphones</t>
         </is>
       </c>
       <c r="C205" s="8"/>
@@ -4729,12 +4707,12 @@
     <row r="206">
       <c r="A206" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3105</t>
+          <t xml:space="preserve">1918</t>
         </is>
       </c>
       <c r="B206" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crane &amp; Dailies Grips</t>
+          <t xml:space="preserve">Playback operator</t>
         </is>
       </c>
       <c r="C206" s="8"/>
@@ -4753,12 +4731,12 @@
     <row r="207">
       <c r="A207" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3106</t>
+          <t xml:space="preserve">1921</t>
         </is>
       </c>
       <c r="B207" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standby Stage Hand</t>
+          <t xml:space="preserve">Video assist and monitors</t>
         </is>
       </c>
       <c r="C207" s="8"/>
@@ -4777,12 +4755,12 @@
     <row r="208">
       <c r="A208" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3107</t>
+          <t xml:space="preserve">1924</t>
         </is>
       </c>
       <c r="B208" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standby Painter</t>
+          <t xml:space="preserve">Two-way radios</t>
         </is>
       </c>
       <c r="C208" s="8"/>
@@ -4801,12 +4779,12 @@
     <row r="209">
       <c r="A209" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3108</t>
+          <t xml:space="preserve">1927</t>
         </is>
       </c>
       <c r="B209" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standby Carpenter</t>
+          <t xml:space="preserve">Communication licences</t>
         </is>
       </c>
       <c r="C209" s="8"/>
@@ -4825,12 +4803,12 @@
     <row r="210">
       <c r="A210" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3109</t>
+          <t xml:space="preserve">1930</t>
         </is>
       </c>
       <c r="B210" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Standby Rigger</t>
+          <t xml:space="preserve">Sound consumables</t>
         </is>
       </c>
       <c r="C210" s="8"/>
@@ -4847,38 +4825,27 @@
       </c>
     </row>
     <row r="211">
-      <c r="A211" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3110</t>
-        </is>
-      </c>
-      <c r="B211" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rigging Grips</t>
-        </is>
-      </c>
-      <c r="C211" s="8"/>
-      <c r="D211" s="9">
-        <v>0</v>
-      </c>
-      <c r="E211" s="11"/>
-      <c r="F211" s="10">
-        <v>0</v>
-      </c>
-      <c r="G211" s="10">
-        <f>ROUND(D211*F211,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A211" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2000 - Data, Dailies &amp; Media</t>
+        </is>
+      </c>
+      <c r="B211" s="7"/>
+      <c r="C211" s="7"/>
+      <c r="D211" s="7"/>
+      <c r="E211" s="7"/>
+      <c r="F211" s="7"/>
+      <c r="G211" s="7"/>
     </row>
     <row r="212">
       <c r="A212" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3112</t>
+          <t xml:space="preserve">2003</t>
         </is>
       </c>
       <c r="B212" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Medic</t>
+          <t xml:space="preserve">Data manager</t>
         </is>
       </c>
       <c r="C212" s="8"/>
@@ -4897,12 +4864,12 @@
     <row r="213">
       <c r="A213" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3115</t>
+          <t xml:space="preserve">2006</t>
         </is>
       </c>
       <c r="B213" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Fire Cover</t>
+          <t xml:space="preserve">Data wrangler</t>
         </is>
       </c>
       <c r="C213" s="8"/>
@@ -4921,12 +4888,12 @@
     <row r="214">
       <c r="A214" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3118</t>
+          <t xml:space="preserve">2009</t>
         </is>
       </c>
       <c r="B214" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Grip Equipment Rentals</t>
+          <t xml:space="preserve">Dailies colourist</t>
         </is>
       </c>
       <c r="C214" s="8"/>
@@ -4945,12 +4912,12 @@
     <row r="215">
       <c r="A215" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119</t>
+          <t xml:space="preserve">2012</t>
         </is>
       </c>
       <c r="B215" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchases</t>
+          <t xml:space="preserve">On-set storage</t>
         </is>
       </c>
       <c r="C215" s="8"/>
@@ -4969,12 +4936,12 @@
     <row r="216">
       <c r="A216" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3186</t>
+          <t xml:space="preserve">2015</t>
         </is>
       </c>
       <c r="B216" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Health &amp; Safety</t>
+          <t xml:space="preserve">Shuttle drives</t>
         </is>
       </c>
       <c r="C216" s="8"/>
@@ -4993,12 +4960,12 @@
     <row r="217">
       <c r="A217" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3190</t>
+          <t xml:space="preserve">2018</t>
         </is>
       </c>
       <c r="B217" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rental</t>
+          <t xml:space="preserve">Cloud transfer and review</t>
         </is>
       </c>
       <c r="C217" s="8"/>
@@ -5017,12 +4984,12 @@
     <row r="218">
       <c r="A218" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3198</t>
+          <t xml:space="preserve">2021</t>
         </is>
       </c>
       <c r="B218" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Dailies processing</t>
         </is>
       </c>
       <c r="C218" s="8"/>
@@ -5039,51 +5006,51 @@
       </c>
     </row>
     <row r="219">
-      <c r="A219" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3200 - Electrical</t>
-        </is>
-      </c>
-      <c r="B219" s="7"/>
-      <c r="C219" s="7"/>
-      <c r="D219" s="7"/>
-      <c r="E219" s="7"/>
-      <c r="F219" s="7"/>
-      <c r="G219" s="7"/>
+      <c r="A219" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2024</t>
+        </is>
+      </c>
+      <c r="B219" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Long-term production backup</t>
+        </is>
+      </c>
+      <c r="C219" s="8"/>
+      <c r="D219" s="9">
+        <v>0</v>
+      </c>
+      <c r="E219" s="11"/>
+      <c r="F219" s="10">
+        <v>0</v>
+      </c>
+      <c r="G219" s="10">
+        <f>ROUND(D219*F219,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="220">
-      <c r="A220" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3201</t>
-        </is>
-      </c>
-      <c r="B220" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gaffer</t>
-        </is>
-      </c>
-      <c r="C220" s="8"/>
-      <c r="D220" s="9">
-        <v>0</v>
-      </c>
-      <c r="E220" s="11"/>
-      <c r="F220" s="10">
-        <v>0</v>
-      </c>
-      <c r="G220" s="10">
-        <f>ROUND(D220*F220,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A220" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2100 - Transport &amp; Logistics</t>
+        </is>
+      </c>
+      <c r="B220" s="7"/>
+      <c r="C220" s="7"/>
+      <c r="D220" s="7"/>
+      <c r="E220" s="7"/>
+      <c r="F220" s="7"/>
+      <c r="G220" s="7"/>
     </row>
     <row r="221">
       <c r="A221" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3202</t>
+          <t xml:space="preserve">2103</t>
         </is>
       </c>
       <c r="B221" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Best Boy Electric</t>
+          <t xml:space="preserve">Transport coordinator</t>
         </is>
       </c>
       <c r="C221" s="8"/>
@@ -5102,12 +5069,12 @@
     <row r="222">
       <c r="A222" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3203</t>
+          <t xml:space="preserve">2106</t>
         </is>
       </c>
       <c r="B222" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lighting Labour</t>
+          <t xml:space="preserve">Drivers</t>
         </is>
       </c>
       <c r="C222" s="8"/>
@@ -5126,12 +5093,12 @@
     <row r="223">
       <c r="A223" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3204</t>
+          <t xml:space="preserve">2109</t>
         </is>
       </c>
       <c r="B223" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generator Operator</t>
+          <t xml:space="preserve">Crew buses and vans</t>
         </is>
       </c>
       <c r="C223" s="8"/>
@@ -5150,12 +5117,12 @@
     <row r="224">
       <c r="A224" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3206</t>
+          <t xml:space="preserve">2112</t>
         </is>
       </c>
       <c r="B224" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rigging Gaffer</t>
+          <t xml:space="preserve">Equipment trucks</t>
         </is>
       </c>
       <c r="C224" s="8"/>
@@ -5174,12 +5141,12 @@
     <row r="225">
       <c r="A225" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3207</t>
+          <t xml:space="preserve">2115</t>
         </is>
       </c>
       <c r="B225" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rigging Electricians</t>
+          <t xml:space="preserve">Unit and facilities vehicles</t>
         </is>
       </c>
       <c r="C225" s="8"/>
@@ -5198,12 +5165,12 @@
     <row r="226">
       <c r="A226" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3216</t>
+          <t xml:space="preserve">2118</t>
         </is>
       </c>
       <c r="B226" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Lighting Consumables</t>
+          <t xml:space="preserve">Self-drive vehicles</t>
         </is>
       </c>
       <c r="C226" s="8"/>
@@ -5222,12 +5189,12 @@
     <row r="227">
       <c r="A227" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3218</t>
+          <t xml:space="preserve">2121</t>
         </is>
       </c>
       <c r="B227" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Main Lighting Package</t>
+          <t xml:space="preserve">Fuel and charging</t>
         </is>
       </c>
       <c r="C227" s="8"/>
@@ -5246,12 +5213,12 @@
     <row r="228">
       <c r="A228" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3298</t>
+          <t xml:space="preserve">2124</t>
         </is>
       </c>
       <c r="B228" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Mileage and parking</t>
         </is>
       </c>
       <c r="C228" s="8"/>
@@ -5268,27 +5235,38 @@
       </c>
     </row>
     <row r="229">
-      <c r="A229" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3300 - Wardrobe</t>
-        </is>
-      </c>
-      <c r="B229" s="7"/>
-      <c r="C229" s="7"/>
-      <c r="D229" s="7"/>
-      <c r="E229" s="7"/>
-      <c r="F229" s="7"/>
-      <c r="G229" s="7"/>
+      <c r="A229" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2127</t>
+        </is>
+      </c>
+      <c r="B229" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vehicle permits and tolls</t>
+        </is>
+      </c>
+      <c r="C229" s="8"/>
+      <c r="D229" s="9">
+        <v>0</v>
+      </c>
+      <c r="E229" s="11"/>
+      <c r="F229" s="10">
+        <v>0</v>
+      </c>
+      <c r="G229" s="10">
+        <f>ROUND(D229*F229,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="230">
       <c r="A230" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3301</t>
+          <t xml:space="preserve">2130</t>
         </is>
       </c>
       <c r="B230" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Designer</t>
+          <t xml:space="preserve">Vehicle repairs and cleaning</t>
         </is>
       </c>
       <c r="C230" s="8"/>
@@ -5307,12 +5285,12 @@
     <row r="231">
       <c r="A231" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3303</t>
+          <t xml:space="preserve">2133</t>
         </is>
       </c>
       <c r="B231" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Supervisor</t>
+          <t xml:space="preserve">Freight and couriers</t>
         </is>
       </c>
       <c r="C231" s="8"/>
@@ -5331,12 +5309,12 @@
     <row r="232">
       <c r="A232" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3304</t>
+          <t xml:space="preserve">2136</t>
         </is>
       </c>
       <c r="B232" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Buyer</t>
+          <t xml:space="preserve">Transport loss and damage allowance</t>
         </is>
       </c>
       <c r="C232" s="8"/>
@@ -5353,38 +5331,27 @@
       </c>
     </row>
     <row r="233">
-      <c r="A233" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3305</t>
-        </is>
-      </c>
-      <c r="B233" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Costume Stand Bys</t>
-        </is>
-      </c>
-      <c r="C233" s="8"/>
-      <c r="D233" s="9">
-        <v>0</v>
-      </c>
-      <c r="E233" s="11"/>
-      <c r="F233" s="10">
-        <v>0</v>
-      </c>
-      <c r="G233" s="10">
-        <f>ROUND(D233*F233,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A233" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2200 - Catering, Welfare &amp; Unit Services</t>
+        </is>
+      </c>
+      <c r="B233" s="7"/>
+      <c r="C233" s="7"/>
+      <c r="D233" s="7"/>
+      <c r="E233" s="7"/>
+      <c r="F233" s="7"/>
+      <c r="G233" s="7"/>
     </row>
     <row r="234">
       <c r="A234" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3308</t>
+          <t xml:space="preserve">2203</t>
         </is>
       </c>
       <c r="B234" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Assistants</t>
+          <t xml:space="preserve">Crew catering</t>
         </is>
       </c>
       <c r="C234" s="8"/>
@@ -5403,12 +5370,12 @@
     <row r="235">
       <c r="A235" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3309</t>
+          <t xml:space="preserve">2206</t>
         </is>
       </c>
       <c r="B235" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Dailies</t>
+          <t xml:space="preserve">Craft service</t>
         </is>
       </c>
       <c r="C235" s="8"/>
@@ -5427,12 +5394,12 @@
     <row r="236">
       <c r="A236" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3315</t>
+          <t xml:space="preserve">2209</t>
         </is>
       </c>
       <c r="B236" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Manufacture</t>
+          <t xml:space="preserve">Drinking water</t>
         </is>
       </c>
       <c r="C236" s="8"/>
@@ -5451,12 +5418,12 @@
     <row r="237">
       <c r="A237" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3316</t>
+          <t xml:space="preserve">2212</t>
         </is>
       </c>
       <c r="B237" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Costume Purchases &amp; Rentals</t>
+          <t xml:space="preserve">Dining tents and furniture</t>
         </is>
       </c>
       <c r="C237" s="8"/>
@@ -5475,12 +5442,12 @@
     <row r="238">
       <c r="A238" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3376</t>
+          <t xml:space="preserve">2215</t>
         </is>
       </c>
       <c r="B238" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wardrobe Shop Rental</t>
+          <t xml:space="preserve">Mobile toilets and washrooms</t>
         </is>
       </c>
       <c r="C238" s="8"/>
@@ -5499,12 +5466,12 @@
     <row r="239">
       <c r="A239" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3385</t>
+          <t xml:space="preserve">2218</t>
         </is>
       </c>
       <c r="B239" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other Costs</t>
+          <t xml:space="preserve">Waste and recycling service</t>
         </is>
       </c>
       <c r="C239" s="8"/>
@@ -5523,12 +5490,12 @@
     <row r="240">
       <c r="A240" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3390</t>
+          <t xml:space="preserve">2221</t>
         </is>
       </c>
       <c r="B240" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Unit cleaning</t>
         </is>
       </c>
       <c r="C240" s="8"/>
@@ -5547,12 +5514,12 @@
     <row r="241">
       <c r="A241" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3398</t>
+          <t xml:space="preserve">2224</t>
         </is>
       </c>
       <c r="B241" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Crew welfare supplies</t>
         </is>
       </c>
       <c r="C241" s="8"/>
@@ -5569,51 +5536,51 @@
       </c>
     </row>
     <row r="242">
-      <c r="A242" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3400 - Make-Up &amp; Hairdressing</t>
-        </is>
-      </c>
-      <c r="B242" s="7"/>
-      <c r="C242" s="7"/>
-      <c r="D242" s="7"/>
-      <c r="E242" s="7"/>
-      <c r="F242" s="7"/>
-      <c r="G242" s="7"/>
+      <c r="A242" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2227</t>
+        </is>
+      </c>
+      <c r="B242" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">On-set medical cover</t>
+        </is>
+      </c>
+      <c r="C242" s="8"/>
+      <c r="D242" s="9">
+        <v>0</v>
+      </c>
+      <c r="E242" s="11"/>
+      <c r="F242" s="10">
+        <v>0</v>
+      </c>
+      <c r="G242" s="10">
+        <f>ROUND(D242*F242,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="243">
-      <c r="A243" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3401</t>
-        </is>
-      </c>
-      <c r="B243" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Make-Up &amp; Hair Designer</t>
-        </is>
-      </c>
-      <c r="C243" s="8"/>
-      <c r="D243" s="9">
-        <v>0</v>
-      </c>
-      <c r="E243" s="11"/>
-      <c r="F243" s="10">
-        <v>0</v>
-      </c>
-      <c r="G243" s="10">
-        <f>ROUND(D243*F243,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A243" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2300 - Stunts, Animals &amp; Physical Effects</t>
+        </is>
+      </c>
+      <c r="B243" s="7"/>
+      <c r="C243" s="7"/>
+      <c r="D243" s="7"/>
+      <c r="E243" s="7"/>
+      <c r="F243" s="7"/>
+      <c r="G243" s="7"/>
     </row>
     <row r="244">
       <c r="A244" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3402</t>
+          <t xml:space="preserve">2303</t>
         </is>
       </c>
       <c r="B244" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make-Up &amp; Hair Artists</t>
+          <t xml:space="preserve">Stunt coordinator</t>
         </is>
       </c>
       <c r="C244" s="8"/>
@@ -5632,12 +5599,12 @@
     <row r="245">
       <c r="A245" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3403</t>
+          <t xml:space="preserve">2306</t>
         </is>
       </c>
       <c r="B245" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Additional Make-Up &amp; Hair Labour</t>
+          <t xml:space="preserve">Stunt performers</t>
         </is>
       </c>
       <c r="C245" s="8"/>
@@ -5656,12 +5623,12 @@
     <row r="246">
       <c r="A246" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3405</t>
+          <t xml:space="preserve">2309</t>
         </is>
       </c>
       <c r="B246" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Prosthetics</t>
+          <t xml:space="preserve">Stunt rehearsal and training</t>
         </is>
       </c>
       <c r="C246" s="8"/>
@@ -5680,12 +5647,12 @@
     <row r="247">
       <c r="A247" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3414</t>
+          <t xml:space="preserve">2312</t>
         </is>
       </c>
       <c r="B247" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Wigs &amp; Hairpieces</t>
+          <t xml:space="preserve">Stunt equipment</t>
         </is>
       </c>
       <c r="C247" s="8"/>
@@ -5704,12 +5671,12 @@
     <row r="248">
       <c r="A248" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3416</t>
+          <t xml:space="preserve">2315</t>
         </is>
       </c>
       <c r="B248" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Make Up Purchases</t>
+          <t xml:space="preserve">Animal coordinator and handlers</t>
         </is>
       </c>
       <c r="C248" s="8"/>
@@ -5728,12 +5695,12 @@
     <row r="249">
       <c r="A249" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3417</t>
+          <t xml:space="preserve">2318</t>
         </is>
       </c>
       <c r="B249" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Animals and animal transport</t>
         </is>
       </c>
       <c r="C249" s="8"/>
@@ -5750,27 +5717,38 @@
       </c>
     </row>
     <row r="250">
-      <c r="A250" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3500 - Sound &amp; Video</t>
-        </is>
-      </c>
-      <c r="B250" s="7"/>
-      <c r="C250" s="7"/>
-      <c r="D250" s="7"/>
-      <c r="E250" s="7"/>
-      <c r="F250" s="7"/>
-      <c r="G250" s="7"/>
+      <c r="A250" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2321</t>
+        </is>
+      </c>
+      <c r="B250" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Animal welfare support</t>
+        </is>
+      </c>
+      <c r="C250" s="8"/>
+      <c r="D250" s="9">
+        <v>0</v>
+      </c>
+      <c r="E250" s="11"/>
+      <c r="F250" s="10">
+        <v>0</v>
+      </c>
+      <c r="G250" s="10">
+        <f>ROUND(D250*F250,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="251">
       <c r="A251" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3501</t>
+          <t xml:space="preserve">2324</t>
         </is>
       </c>
       <c r="B251" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound Mixer</t>
+          <t xml:space="preserve">Physical effects supervisor</t>
         </is>
       </c>
       <c r="C251" s="8"/>
@@ -5789,12 +5767,12 @@
     <row r="252">
       <c r="A252" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3502</t>
+          <t xml:space="preserve">2327</t>
         </is>
       </c>
       <c r="B252" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Boom Operator</t>
+          <t xml:space="preserve">Physical effects crew</t>
         </is>
       </c>
       <c r="C252" s="8"/>
@@ -5813,12 +5791,12 @@
     <row r="253">
       <c r="A253" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3503</t>
+          <t xml:space="preserve">2330</t>
         </is>
       </c>
       <c r="B253" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound Assistant/Trainee</t>
+          <t xml:space="preserve">Physical effects materials and rentals</t>
         </is>
       </c>
       <c r="C253" s="8"/>
@@ -5835,38 +5813,27 @@
       </c>
     </row>
     <row r="254">
-      <c r="A254" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3508</t>
-        </is>
-      </c>
-      <c r="B254" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sound Package Rental</t>
-        </is>
-      </c>
-      <c r="C254" s="8"/>
-      <c r="D254" s="9">
-        <v>0</v>
-      </c>
-      <c r="E254" s="11"/>
-      <c r="F254" s="10">
-        <v>0</v>
-      </c>
-      <c r="G254" s="10">
-        <f>ROUND(D254*F254,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A254" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2400 - Specialist Units &amp; Remote Capture</t>
+        </is>
+      </c>
+      <c r="B254" s="7"/>
+      <c r="C254" s="7"/>
+      <c r="D254" s="7"/>
+      <c r="E254" s="7"/>
+      <c r="F254" s="7"/>
+      <c r="G254" s="7"/>
     </row>
     <row r="255">
       <c r="A255" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3510</t>
+          <t xml:space="preserve">2403</t>
         </is>
       </c>
       <c r="B255" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Video Playback Operator</t>
+          <t xml:space="preserve">Second unit crew</t>
         </is>
       </c>
       <c r="C255" s="8"/>
@@ -5885,12 +5852,12 @@
     <row r="256">
       <c r="A256" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3511</t>
+          <t xml:space="preserve">2406</t>
         </is>
       </c>
       <c r="B256" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Video Package Rental</t>
+          <t xml:space="preserve">Splinter unit crew</t>
         </is>
       </c>
       <c r="C256" s="8"/>
@@ -5909,12 +5876,12 @@
     <row r="257">
       <c r="A257" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3516</t>
+          <t xml:space="preserve">2409</t>
         </is>
       </c>
       <c r="B257" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Purchases</t>
+          <t xml:space="preserve">Documentary field unit</t>
         </is>
       </c>
       <c r="C257" s="8"/>
@@ -5933,12 +5900,12 @@
     <row r="258">
       <c r="A258" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3528</t>
+          <t xml:space="preserve">2412</t>
         </is>
       </c>
       <c r="B258" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Walkie Talkies</t>
+          <t xml:space="preserve">Remote production kit</t>
         </is>
       </c>
       <c r="C258" s="8"/>
@@ -5957,12 +5924,12 @@
     <row r="259">
       <c r="A259" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3598</t>
+          <t xml:space="preserve">2415</t>
         </is>
       </c>
       <c r="B259" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Marine unit</t>
         </is>
       </c>
       <c r="C259" s="8"/>
@@ -5979,27 +5946,38 @@
       </c>
     </row>
     <row r="260">
-      <c r="A260" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3600 - Transportation</t>
-        </is>
-      </c>
-      <c r="B260" s="7"/>
-      <c r="C260" s="7"/>
-      <c r="D260" s="7"/>
-      <c r="E260" s="7"/>
-      <c r="F260" s="7"/>
-      <c r="G260" s="7"/>
+      <c r="A260" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2418</t>
+        </is>
+      </c>
+      <c r="B260" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aerial unit</t>
+        </is>
+      </c>
+      <c r="C260" s="8"/>
+      <c r="D260" s="9">
+        <v>0</v>
+      </c>
+      <c r="E260" s="11"/>
+      <c r="F260" s="10">
+        <v>0</v>
+      </c>
+      <c r="G260" s="10">
+        <f>ROUND(D260*F260,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="261">
       <c r="A261" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3601</t>
+          <t xml:space="preserve">2421</t>
         </is>
       </c>
       <c r="B261" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Manager</t>
+          <t xml:space="preserve">Motion control unit</t>
         </is>
       </c>
       <c r="C261" s="8"/>
@@ -6018,12 +5996,12 @@
     <row r="262">
       <c r="A262" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3602</t>
+          <t xml:space="preserve">2424</t>
         </is>
       </c>
       <c r="B262" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transportation Captain</t>
+          <t xml:space="preserve">Specialist unit travel and logistics</t>
         </is>
       </c>
       <c r="C262" s="8"/>
@@ -6040,38 +6018,27 @@
       </c>
     </row>
     <row r="263">
-      <c r="A263" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3603</t>
-        </is>
-      </c>
-      <c r="B263" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Unit Drivers</t>
-        </is>
-      </c>
-      <c r="C263" s="8"/>
-      <c r="D263" s="9">
-        <v>0</v>
-      </c>
-      <c r="E263" s="11"/>
-      <c r="F263" s="10">
-        <v>0</v>
-      </c>
-      <c r="G263" s="10">
-        <f>ROUND(D263*F263,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A263" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2500 - Editorial &amp; Post Management</t>
+        </is>
+      </c>
+      <c r="B263" s="7"/>
+      <c r="C263" s="7"/>
+      <c r="D263" s="7"/>
+      <c r="E263" s="7"/>
+      <c r="F263" s="7"/>
+      <c r="G263" s="7"/>
     </row>
     <row r="264">
       <c r="A264" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3615</t>
+          <t xml:space="preserve">2503</t>
         </is>
       </c>
       <c r="B264" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crew Minibuses &amp; Coaches</t>
+          <t xml:space="preserve">Post-production producer</t>
         </is>
       </c>
       <c r="C264" s="8"/>
@@ -6090,12 +6057,12 @@
     <row r="265">
       <c r="A265" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3617</t>
+          <t xml:space="preserve">2506</t>
         </is>
       </c>
       <c r="B265" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Equipment Vehicles</t>
+          <t xml:space="preserve">Post-production supervisor</t>
         </is>
       </c>
       <c r="C265" s="8"/>
@@ -6114,12 +6081,12 @@
     <row r="266">
       <c r="A266" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3619</t>
+          <t xml:space="preserve">2509</t>
         </is>
       </c>
       <c r="B266" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Self Drives</t>
+          <t xml:space="preserve">Post-production coordinator</t>
         </is>
       </c>
       <c r="C266" s="8"/>
@@ -6138,12 +6105,12 @@
     <row r="267">
       <c r="A267" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3621</t>
+          <t xml:space="preserve">2512</t>
         </is>
       </c>
       <c r="B267" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Facilities Vehicles</t>
+          <t xml:space="preserve">Editor</t>
         </is>
       </c>
       <c r="C267" s="8"/>
@@ -6162,12 +6129,12 @@
     <row r="268">
       <c r="A268" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3644</t>
+          <t xml:space="preserve">2515</t>
         </is>
       </c>
       <c r="B268" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Petrol &amp; Oil</t>
+          <t xml:space="preserve">Assistant editors</t>
         </is>
       </c>
       <c r="C268" s="8"/>
@@ -6186,12 +6153,12 @@
     <row r="269">
       <c r="A269" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3646</t>
+          <t xml:space="preserve">2518</t>
         </is>
       </c>
       <c r="B269" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Repairs &amp; Maintenance</t>
+          <t xml:space="preserve">Editorial rooms</t>
         </is>
       </c>
       <c r="C269" s="8"/>
@@ -6210,12 +6177,12 @@
     <row r="270">
       <c r="A270" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3647</t>
+          <t xml:space="preserve">2521</t>
         </is>
       </c>
       <c r="B270" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Parking &amp; Mileage</t>
+          <t xml:space="preserve">Editing systems and storage</t>
         </is>
       </c>
       <c r="C270" s="8"/>
@@ -6234,12 +6201,12 @@
     <row r="271">
       <c r="A271" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3653</t>
+          <t xml:space="preserve">2524</t>
         </is>
       </c>
       <c r="B271" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bikes &amp; Taxis</t>
+          <t xml:space="preserve">Offline edit</t>
         </is>
       </c>
       <c r="C271" s="8"/>
@@ -6258,12 +6225,12 @@
     <row r="272">
       <c r="A272" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3685</t>
+          <t xml:space="preserve">2527</t>
         </is>
       </c>
       <c r="B272" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Relief Drivers</t>
+          <t xml:space="preserve">Online edit and conform</t>
         </is>
       </c>
       <c r="C272" s="8"/>
@@ -6282,12 +6249,12 @@
     <row r="273">
       <c r="A273" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3698</t>
+          <t xml:space="preserve">2530</t>
         </is>
       </c>
       <c r="B273" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loss &amp; Damage</t>
+          <t xml:space="preserve">Post-production project management</t>
         </is>
       </c>
       <c r="C273" s="8"/>
@@ -6304,51 +6271,51 @@
       </c>
     </row>
     <row r="274">
-      <c r="A274" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3700 - Locations &amp; BTL Travel/Living</t>
-        </is>
-      </c>
-      <c r="B274" s="7"/>
-      <c r="C274" s="7"/>
-      <c r="D274" s="7"/>
-      <c r="E274" s="7"/>
-      <c r="F274" s="7"/>
-      <c r="G274" s="7"/>
+      <c r="A274" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2533</t>
+        </is>
+      </c>
+      <c r="B274" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Post couriers and transfers</t>
+        </is>
+      </c>
+      <c r="C274" s="8"/>
+      <c r="D274" s="9">
+        <v>0</v>
+      </c>
+      <c r="E274" s="11"/>
+      <c r="F274" s="10">
+        <v>0</v>
+      </c>
+      <c r="G274" s="10">
+        <f>ROUND(D274*F274,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="275">
-      <c r="A275" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3701</t>
-        </is>
-      </c>
-      <c r="B275" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Airfares</t>
-        </is>
-      </c>
-      <c r="C275" s="8"/>
-      <c r="D275" s="9">
-        <v>0</v>
-      </c>
-      <c r="E275" s="11"/>
-      <c r="F275" s="10">
-        <v>0</v>
-      </c>
-      <c r="G275" s="10">
-        <f>ROUND(D275*F275,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A275" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2600 - Post Sound &amp; Voice Recording</t>
+        </is>
+      </c>
+      <c r="B275" s="7"/>
+      <c r="C275" s="7"/>
+      <c r="D275" s="7"/>
+      <c r="E275" s="7"/>
+      <c r="F275" s="7"/>
+      <c r="G275" s="7"/>
     </row>
     <row r="276">
       <c r="A276" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3704</t>
+          <t xml:space="preserve">2603</t>
         </is>
       </c>
       <c r="B276" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hotel &amp; Living</t>
+          <t xml:space="preserve">Supervising sound editor</t>
         </is>
       </c>
       <c r="C276" s="8"/>
@@ -6367,12 +6334,12 @@
     <row r="277">
       <c r="A277" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3706</t>
+          <t xml:space="preserve">2606</t>
         </is>
       </c>
       <c r="B277" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Scouting/Survey Costs</t>
+          <t xml:space="preserve">Dialogue editing</t>
         </is>
       </c>
       <c r="C277" s="8"/>
@@ -6391,12 +6358,12 @@
     <row r="278">
       <c r="A278" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3707</t>
+          <t xml:space="preserve">2609</t>
         </is>
       </c>
       <c r="B278" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location Site Rental Fees</t>
+          <t xml:space="preserve">Sound effects editing</t>
         </is>
       </c>
       <c r="C278" s="8"/>
@@ -6415,12 +6382,12 @@
     <row r="279">
       <c r="A279" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3708</t>
+          <t xml:space="preserve">2612</t>
         </is>
       </c>
       <c r="B279" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base Camps &amp; Tech Parking</t>
+          <t xml:space="preserve">ADR recording</t>
         </is>
       </c>
       <c r="C279" s="8"/>
@@ -6439,12 +6406,12 @@
     <row r="280">
       <c r="A280" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3709</t>
+          <t xml:space="preserve">2615</t>
         </is>
       </c>
       <c r="B280" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Gratuities</t>
+          <t xml:space="preserve">Foley recording</t>
         </is>
       </c>
       <c r="C280" s="8"/>
@@ -6463,12 +6430,12 @@
     <row r="281">
       <c r="A281" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3710</t>
+          <t xml:space="preserve">2618</t>
         </is>
       </c>
       <c r="B281" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location Equipment</t>
+          <t xml:space="preserve">Voice-over recording</t>
         </is>
       </c>
       <c r="C281" s="8"/>
@@ -6487,12 +6454,12 @@
     <row r="282">
       <c r="A282" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3713</t>
+          <t xml:space="preserve">2621</t>
         </is>
       </c>
       <c r="B282" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Shipping - Fed Ex, Freight</t>
+          <t xml:space="preserve">Premix</t>
         </is>
       </c>
       <c r="C282" s="8"/>
@@ -6511,12 +6478,12 @@
     <row r="283">
       <c r="A283" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3720</t>
+          <t xml:space="preserve">2624</t>
         </is>
       </c>
       <c r="B283" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Location Catering</t>
+          <t xml:space="preserve">Final mix</t>
         </is>
       </c>
       <c r="C283" s="8"/>
@@ -6535,12 +6502,12 @@
     <row r="284">
       <c r="A284" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3722</t>
+          <t xml:space="preserve">2627</t>
         </is>
       </c>
       <c r="B284" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Dining &amp; Crowd Marquees</t>
+          <t xml:space="preserve">Audio layback and quality control</t>
         </is>
       </c>
       <c r="C284" s="8"/>
@@ -6557,38 +6524,27 @@
       </c>
     </row>
     <row r="285">
-      <c r="A285" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3730</t>
-        </is>
-      </c>
-      <c r="B285" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Security &amp; Police</t>
-        </is>
-      </c>
-      <c r="C285" s="8"/>
-      <c r="D285" s="9">
-        <v>0</v>
-      </c>
-      <c r="E285" s="11"/>
-      <c r="F285" s="10">
-        <v>0</v>
-      </c>
-      <c r="G285" s="10">
-        <f>ROUND(D285*F285,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A285" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2700 - Music &amp; Music Rights</t>
+        </is>
+      </c>
+      <c r="B285" s="7"/>
+      <c r="C285" s="7"/>
+      <c r="D285" s="7"/>
+      <c r="E285" s="7"/>
+      <c r="F285" s="7"/>
+      <c r="G285" s="7"/>
     </row>
     <row r="286">
       <c r="A286" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3741</t>
+          <t xml:space="preserve">2703</t>
         </is>
       </c>
       <c r="B286" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Photocopier Rental</t>
+          <t xml:space="preserve">Composer</t>
         </is>
       </c>
       <c r="C286" s="8"/>
@@ -6607,12 +6563,12 @@
     <row r="287">
       <c r="A287" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3742</t>
+          <t xml:space="preserve">2706</t>
         </is>
       </c>
       <c r="B287" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Telephones</t>
+          <t xml:space="preserve">Music supervisor</t>
         </is>
       </c>
       <c r="C287" s="8"/>
@@ -6631,12 +6587,12 @@
     <row r="288">
       <c r="A288" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3743</t>
+          <t xml:space="preserve">2709</t>
         </is>
       </c>
       <c r="B288" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mobile Phones</t>
+          <t xml:space="preserve">Music editor</t>
         </is>
       </c>
       <c r="C288" s="8"/>
@@ -6655,12 +6611,12 @@
     <row r="289">
       <c r="A289" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3746</t>
+          <t xml:space="preserve">2712</t>
         </is>
       </c>
       <c r="B289" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stationery &amp; Postage</t>
+          <t xml:space="preserve">Musicians and vocalists</t>
         </is>
       </c>
       <c r="C289" s="8"/>
@@ -6679,12 +6635,12 @@
     <row r="290">
       <c r="A290" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3798</t>
+          <t xml:space="preserve">2715</t>
         </is>
       </c>
       <c r="B290" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Other</t>
+          <t xml:space="preserve">Recording studio</t>
         </is>
       </c>
       <c r="C290" s="8"/>
@@ -6701,27 +6657,38 @@
       </c>
     </row>
     <row r="291">
-      <c r="A291" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3800 - Digital Media &amp; Stock</t>
-        </is>
-      </c>
-      <c r="B291" s="7"/>
-      <c r="C291" s="7"/>
-      <c r="D291" s="7"/>
-      <c r="E291" s="7"/>
-      <c r="F291" s="7"/>
-      <c r="G291" s="7"/>
+      <c r="A291" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2718</t>
+        </is>
+      </c>
+      <c r="B291" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Orchestration and copying</t>
+        </is>
+      </c>
+      <c r="C291" s="8"/>
+      <c r="D291" s="9">
+        <v>0</v>
+      </c>
+      <c r="E291" s="11"/>
+      <c r="F291" s="10">
+        <v>0</v>
+      </c>
+      <c r="G291" s="10">
+        <f>ROUND(D291*F291,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="292">
       <c r="A292" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3801</t>
+          <t xml:space="preserve">2721</t>
         </is>
       </c>
       <c r="B292" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Hard Drives &amp; Storage</t>
+          <t xml:space="preserve">Original score mixing</t>
         </is>
       </c>
       <c r="C292" s="8"/>
@@ -6740,12 +6707,12 @@
     <row r="293">
       <c r="A293" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3805</t>
+          <t xml:space="preserve">2724</t>
         </is>
       </c>
       <c r="B293" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Rushes Drives</t>
+          <t xml:space="preserve">Music licences</t>
         </is>
       </c>
       <c r="C293" s="8"/>
@@ -6762,51 +6729,51 @@
       </c>
     </row>
     <row r="294">
-      <c r="A294" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3806</t>
-        </is>
-      </c>
-      <c r="B294" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Rushes Transfers &amp; Uploads</t>
-        </is>
-      </c>
-      <c r="C294" s="8"/>
-      <c r="D294" s="9">
-        <v>0</v>
-      </c>
-      <c r="E294" s="11"/>
-      <c r="F294" s="10">
-        <v>0</v>
-      </c>
-      <c r="G294" s="10">
-        <f>ROUND(D294*F294,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A294" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2800 - VFX, Animation &amp; Motion Graphics</t>
+        </is>
+      </c>
+      <c r="B294" s="7"/>
+      <c r="C294" s="7"/>
+      <c r="D294" s="7"/>
+      <c r="E294" s="7"/>
+      <c r="F294" s="7"/>
+      <c r="G294" s="7"/>
     </row>
     <row r="295">
-      <c r="A295" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3900 - Additional Hours</t>
-        </is>
-      </c>
-      <c r="B295" s="7"/>
-      <c r="C295" s="7"/>
-      <c r="D295" s="7"/>
-      <c r="E295" s="7"/>
-      <c r="F295" s="7"/>
-      <c r="G295" s="7"/>
+      <c r="A295" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2803</t>
+        </is>
+      </c>
+      <c r="B295" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual effects supervisor</t>
+        </is>
+      </c>
+      <c r="C295" s="8"/>
+      <c r="D295" s="9">
+        <v>0</v>
+      </c>
+      <c r="E295" s="11"/>
+      <c r="F295" s="10">
+        <v>0</v>
+      </c>
+      <c r="G295" s="10">
+        <f>ROUND(D295*F295,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="296">
       <c r="A296" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">3900</t>
+          <t xml:space="preserve">2806</t>
         </is>
       </c>
       <c r="B296" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Overtime</t>
+          <t xml:space="preserve">On-set visual effects support</t>
         </is>
       </c>
       <c r="C296" s="8"/>
@@ -6823,27 +6790,38 @@
       </c>
     </row>
     <row r="297">
-      <c r="A297" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4000 - 2nd Unit</t>
-        </is>
-      </c>
-      <c r="B297" s="7"/>
-      <c r="C297" s="7"/>
-      <c r="D297" s="7"/>
-      <c r="E297" s="7"/>
-      <c r="F297" s="7"/>
-      <c r="G297" s="7"/>
+      <c r="A297" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2809</t>
+        </is>
+      </c>
+      <c r="B297" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Visual effects production</t>
+        </is>
+      </c>
+      <c r="C297" s="8"/>
+      <c r="D297" s="9">
+        <v>0</v>
+      </c>
+      <c r="E297" s="11"/>
+      <c r="F297" s="10">
+        <v>0</v>
+      </c>
+      <c r="G297" s="10">
+        <f>ROUND(D297*F297,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="298">
       <c r="A298" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4001</t>
+          <t xml:space="preserve">2812</t>
         </is>
       </c>
       <c r="B298" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2nd Unit</t>
+          <t xml:space="preserve">Compositing and cleanup</t>
         </is>
       </c>
       <c r="C298" s="8"/>
@@ -6862,12 +6840,12 @@
     <row r="299">
       <c r="A299" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4002</t>
+          <t xml:space="preserve">2815</t>
         </is>
       </c>
       <c r="B299" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Camera Operator</t>
+          <t xml:space="preserve">3D and animation</t>
         </is>
       </c>
       <c r="C299" s="8"/>
@@ -6886,12 +6864,12 @@
     <row r="300">
       <c r="A300" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4003</t>
+          <t xml:space="preserve">2818</t>
         </is>
       </c>
       <c r="B300" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Focus Puller</t>
+          <t xml:space="preserve">Motion graphics</t>
         </is>
       </c>
       <c r="C300" s="8"/>
@@ -6910,12 +6888,12 @@
     <row r="301">
       <c r="A301" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4004</t>
+          <t xml:space="preserve">2821</t>
         </is>
       </c>
       <c r="B301" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Assistant Camera</t>
+          <t xml:space="preserve">Screen replacements</t>
         </is>
       </c>
       <c r="C301" s="8"/>
@@ -6934,12 +6912,12 @@
     <row r="302">
       <c r="A302" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4005</t>
+          <t xml:space="preserve">2824</t>
         </is>
       </c>
       <c r="B302" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Data Wrangler</t>
+          <t xml:space="preserve">Visual effects storage and transfer</t>
         </is>
       </c>
       <c r="C302" s="8"/>
@@ -6958,12 +6936,12 @@
     <row r="303">
       <c r="A303" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4006</t>
+          <t xml:space="preserve">2827</t>
         </is>
       </c>
       <c r="B303" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Soundman And Boom</t>
+          <t xml:space="preserve">Visual effects review and quality control</t>
         </is>
       </c>
       <c r="C303" s="8"/>
@@ -6980,38 +6958,27 @@
       </c>
     </row>
     <row r="304">
-      <c r="A304" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4007</t>
-        </is>
-      </c>
-      <c r="B304" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Third Assistant Director</t>
-        </is>
-      </c>
-      <c r="C304" s="8"/>
-      <c r="D304" s="9">
-        <v>0</v>
-      </c>
-      <c r="E304" s="11"/>
-      <c r="F304" s="10">
-        <v>0</v>
-      </c>
-      <c r="G304" s="10">
-        <f>ROUND(D304*F304,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A304" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2900 - Colour, Finishing &amp; Mastering</t>
+        </is>
+      </c>
+      <c r="B304" s="7"/>
+      <c r="C304" s="7"/>
+      <c r="D304" s="7"/>
+      <c r="E304" s="7"/>
+      <c r="F304" s="7"/>
+      <c r="G304" s="7"/>
     </row>
     <row r="305">
       <c r="A305" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4008</t>
+          <t xml:space="preserve">2903</t>
         </is>
       </c>
       <c r="B305" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Dailies</t>
+          <t xml:space="preserve">Picture conform</t>
         </is>
       </c>
       <c r="C305" s="8"/>
@@ -7030,12 +6997,12 @@
     <row r="306">
       <c r="A306" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4009</t>
+          <t xml:space="preserve">2906</t>
         </is>
       </c>
       <c r="B306" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Chaperone</t>
+          <t xml:space="preserve">Colour grading</t>
         </is>
       </c>
       <c r="C306" s="8"/>
@@ -7054,12 +7021,12 @@
     <row r="307">
       <c r="A307" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4010</t>
+          <t xml:space="preserve">2909</t>
         </is>
       </c>
       <c r="B307" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Medic</t>
+          <t xml:space="preserve">Online finishing</t>
         </is>
       </c>
       <c r="C307" s="8"/>
@@ -7078,12 +7045,12 @@
     <row r="308">
       <c r="A308" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4011</t>
+          <t xml:space="preserve">2912</t>
         </is>
       </c>
       <c r="B308" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Box Rentals</t>
+          <t xml:space="preserve">Restoration and cleanup</t>
         </is>
       </c>
       <c r="C308" s="8"/>
@@ -7102,12 +7069,12 @@
     <row r="309">
       <c r="A309" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4012</t>
+          <t xml:space="preserve">2915</t>
         </is>
       </c>
       <c r="B309" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Camera Equipment</t>
+          <t xml:space="preserve">Mastering</t>
         </is>
       </c>
       <c r="C309" s="8"/>
@@ -7126,12 +7093,12 @@
     <row r="310">
       <c r="A310" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4013</t>
+          <t xml:space="preserve">2918</t>
         </is>
       </c>
       <c r="B310" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Second Unit Grips Equipment</t>
+          <t xml:space="preserve">Picture quality control</t>
         </is>
       </c>
       <c r="C310" s="8"/>
@@ -7150,12 +7117,12 @@
     <row r="311">
       <c r="A311" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4014</t>
+          <t xml:space="preserve">2921</t>
         </is>
       </c>
       <c r="B311" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound Equipment</t>
+          <t xml:space="preserve">Cinema master</t>
         </is>
       </c>
       <c r="C311" s="8"/>
@@ -7174,12 +7141,12 @@
     <row r="312">
       <c r="A312" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4015</t>
+          <t xml:space="preserve">2924</t>
         </is>
       </c>
       <c r="B312" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Base And Tech Camps</t>
+          <t xml:space="preserve">Broadcast and streaming masters</t>
         </is>
       </c>
       <c r="C312" s="8"/>
@@ -7196,51 +7163,51 @@
       </c>
     </row>
     <row r="313">
-      <c r="A313" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4016</t>
-        </is>
-      </c>
-      <c r="B313" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Catering</t>
-        </is>
-      </c>
-      <c r="C313" s="8"/>
-      <c r="D313" s="9">
-        <v>0</v>
-      </c>
-      <c r="E313" s="11"/>
-      <c r="F313" s="10">
-        <v>0</v>
-      </c>
-      <c r="G313" s="10">
-        <f>ROUND(D313*F313,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A313" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3000 - Deliverables, Access &amp; Localisation</t>
+        </is>
+      </c>
+      <c r="B313" s="7"/>
+      <c r="C313" s="7"/>
+      <c r="D313" s="7"/>
+      <c r="E313" s="7"/>
+      <c r="F313" s="7"/>
+      <c r="G313" s="7"/>
     </row>
     <row r="314">
-      <c r="A314" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4100 - Special Units</t>
-        </is>
-      </c>
-      <c r="B314" s="7"/>
-      <c r="C314" s="7"/>
-      <c r="D314" s="7"/>
-      <c r="E314" s="7"/>
-      <c r="F314" s="7"/>
-      <c r="G314" s="7"/>
+      <c r="A314" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3003</t>
+        </is>
+      </c>
+      <c r="B314" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Delivery management</t>
+        </is>
+      </c>
+      <c r="C314" s="8"/>
+      <c r="D314" s="9">
+        <v>0</v>
+      </c>
+      <c r="E314" s="11"/>
+      <c r="F314" s="10">
+        <v>0</v>
+      </c>
+      <c r="G314" s="10">
+        <f>ROUND(D314*F314,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="315">
       <c r="A315" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">4107</t>
+          <t xml:space="preserve">3006</t>
         </is>
       </c>
       <c r="B315" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Transport</t>
+          <t xml:space="preserve">Technical specifications and packaging</t>
         </is>
       </c>
       <c r="C315" s="8"/>
@@ -7257,27 +7224,38 @@
       </c>
     </row>
     <row r="316">
-      <c r="A316" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5500 - Editing</t>
-        </is>
-      </c>
-      <c r="B316" s="7"/>
-      <c r="C316" s="7"/>
-      <c r="D316" s="7"/>
-      <c r="E316" s="7"/>
-      <c r="F316" s="7"/>
-      <c r="G316" s="7"/>
+      <c r="A316" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3009</t>
+        </is>
+      </c>
+      <c r="B316" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Captions and subtitles</t>
+        </is>
+      </c>
+      <c r="C316" s="8"/>
+      <c r="D316" s="9">
+        <v>0</v>
+      </c>
+      <c r="E316" s="11"/>
+      <c r="F316" s="10">
+        <v>0</v>
+      </c>
+      <c r="G316" s="10">
+        <f>ROUND(D316*F316,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="317">
       <c r="A317" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5501</t>
+          <t xml:space="preserve">3012</t>
         </is>
       </c>
       <c r="B317" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post Production Producer</t>
+          <t xml:space="preserve">Audio description</t>
         </is>
       </c>
       <c r="C317" s="8"/>
@@ -7296,12 +7274,12 @@
     <row r="318">
       <c r="A318" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5502</t>
+          <t xml:space="preserve">3015</t>
         </is>
       </c>
       <c r="B318" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post Production Supervisor</t>
+          <t xml:space="preserve">Sign-language version</t>
         </is>
       </c>
       <c r="C318" s="8"/>
@@ -7320,12 +7298,12 @@
     <row r="319">
       <c r="A319" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5505</t>
+          <t xml:space="preserve">3018</t>
         </is>
       </c>
       <c r="B319" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post Prod Coordinators</t>
+          <t xml:space="preserve">Dubbing and foreign-language versions</t>
         </is>
       </c>
       <c r="C319" s="8"/>
@@ -7344,12 +7322,12 @@
     <row r="320">
       <c r="A320" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5506</t>
+          <t xml:space="preserve">3021</t>
         </is>
       </c>
       <c r="B320" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">On Line Editing</t>
+          <t xml:space="preserve">Dialogue and music-effects masters</t>
         </is>
       </c>
       <c r="C320" s="8"/>
@@ -7368,12 +7346,12 @@
     <row r="321">
       <c r="A321" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5507</t>
+          <t xml:space="preserve">3024</t>
         </is>
       </c>
       <c r="B321" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editor</t>
+          <t xml:space="preserve">Metadata and cue sheets</t>
         </is>
       </c>
       <c r="C321" s="8"/>
@@ -7392,12 +7370,12 @@
     <row r="322">
       <c r="A322" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5508</t>
+          <t xml:space="preserve">3027</t>
         </is>
       </c>
       <c r="B322" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Asst Editors</t>
+          <t xml:space="preserve">Compliance edits</t>
         </is>
       </c>
       <c r="C322" s="8"/>
@@ -7416,12 +7394,12 @@
     <row r="323">
       <c r="A323" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5518</t>
+          <t xml:space="preserve">3030</t>
         </is>
       </c>
       <c r="B323" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cutting Room Rentals</t>
+          <t xml:space="preserve">Long-term archive masters</t>
         </is>
       </c>
       <c r="C323" s="8"/>
@@ -7438,38 +7416,27 @@
       </c>
     </row>
     <row r="324">
-      <c r="A324" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5535</t>
-        </is>
-      </c>
-      <c r="B324" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Editorial Purchases</t>
-        </is>
-      </c>
-      <c r="C324" s="8"/>
-      <c r="D324" s="9">
-        <v>0</v>
-      </c>
-      <c r="E324" s="11"/>
-      <c r="F324" s="10">
-        <v>0</v>
-      </c>
-      <c r="G324" s="10">
-        <f>ROUND(D324*F324,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A324" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3100 - Publicity, Stills &amp; Audience Materials</t>
+        </is>
+      </c>
+      <c r="B324" s="7"/>
+      <c r="C324" s="7"/>
+      <c r="D324" s="7"/>
+      <c r="E324" s="7"/>
+      <c r="F324" s="7"/>
+      <c r="G324" s="7"/>
     </row>
     <row r="325">
       <c r="A325" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5536</t>
+          <t xml:space="preserve">3103</t>
         </is>
       </c>
       <c r="B325" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Editorial/Avid Rentals</t>
+          <t xml:space="preserve">Unit publicist</t>
         </is>
       </c>
       <c r="C325" s="8"/>
@@ -7488,12 +7455,12 @@
     <row r="326">
       <c r="A326" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5540</t>
+          <t xml:space="preserve">3106</t>
         </is>
       </c>
       <c r="B326" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Archiving</t>
+          <t xml:space="preserve">Behind-the-scenes crew</t>
         </is>
       </c>
       <c r="C326" s="8"/>
@@ -7512,12 +7479,12 @@
     <row r="327">
       <c r="A327" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5541</t>
+          <t xml:space="preserve">3109</t>
         </is>
       </c>
       <c r="B327" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Post Meals</t>
+          <t xml:space="preserve">Publicity stills</t>
         </is>
       </c>
       <c r="C327" s="8"/>
@@ -7536,12 +7503,12 @@
     <row r="328">
       <c r="A328" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5585</t>
+          <t xml:space="preserve">3112</t>
         </is>
       </c>
       <c r="B328" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Couriers &amp; Shipping</t>
+          <t xml:space="preserve">Electronic press kit</t>
         </is>
       </c>
       <c r="C328" s="8"/>
@@ -7558,27 +7525,38 @@
       </c>
     </row>
     <row r="329">
-      <c r="A329" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5600 - Music</t>
-        </is>
-      </c>
-      <c r="B329" s="7"/>
-      <c r="C329" s="7"/>
-      <c r="D329" s="7"/>
-      <c r="E329" s="7"/>
-      <c r="F329" s="7"/>
-      <c r="G329" s="7"/>
+      <c r="A329" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3115</t>
+        </is>
+      </c>
+      <c r="B329" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Trailer and teaser</t>
+        </is>
+      </c>
+      <c r="C329" s="8"/>
+      <c r="D329" s="9">
+        <v>0</v>
+      </c>
+      <c r="E329" s="11"/>
+      <c r="F329" s="10">
+        <v>0</v>
+      </c>
+      <c r="G329" s="10">
+        <f>ROUND(D329*F329,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="330">
       <c r="A330" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5601</t>
+          <t xml:space="preserve">3118</t>
         </is>
       </c>
       <c r="B330" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Composer</t>
+          <t xml:space="preserve">Poster and key art</t>
         </is>
       </c>
       <c r="C330" s="8"/>
@@ -7597,12 +7575,12 @@
     <row r="331">
       <c r="A331" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5602</t>
+          <t xml:space="preserve">3121</t>
         </is>
       </c>
       <c r="B331" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Music Supervisor</t>
+          <t xml:space="preserve">Preview screenings</t>
         </is>
       </c>
       <c r="C331" s="8"/>
@@ -7621,12 +7599,12 @@
     <row r="332">
       <c r="A332" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5604</t>
+          <t xml:space="preserve">3124</t>
         </is>
       </c>
       <c r="B332" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Music Editor</t>
+          <t xml:space="preserve">Festival and market materials</t>
         </is>
       </c>
       <c r="C332" s="8"/>
@@ -7643,38 +7621,27 @@
       </c>
     </row>
     <row r="333">
-      <c r="A333" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5608</t>
-        </is>
-      </c>
-      <c r="B333" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Musicians</t>
-        </is>
-      </c>
-      <c r="C333" s="8"/>
-      <c r="D333" s="9">
-        <v>0</v>
-      </c>
-      <c r="E333" s="11"/>
-      <c r="F333" s="10">
-        <v>0</v>
-      </c>
-      <c r="G333" s="10">
-        <f>ROUND(D333*F333,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A333" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3200 - Insurance, Safety &amp; Risk</t>
+        </is>
+      </c>
+      <c r="B333" s="7"/>
+      <c r="C333" s="7"/>
+      <c r="D333" s="7"/>
+      <c r="E333" s="7"/>
+      <c r="F333" s="7"/>
+      <c r="G333" s="7"/>
     </row>
     <row r="334">
       <c r="A334" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5609</t>
+          <t xml:space="preserve">3203</t>
         </is>
       </c>
       <c r="B334" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Misc. Tracks</t>
+          <t xml:space="preserve">Production insurance</t>
         </is>
       </c>
       <c r="C334" s="8"/>
@@ -7693,12 +7660,12 @@
     <row r="335">
       <c r="A335" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5610</t>
+          <t xml:space="preserve">3206</t>
         </is>
       </c>
       <c r="B335" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Music Rights/Licenses</t>
+          <t xml:space="preserve">Equipment insurance</t>
         </is>
       </c>
       <c r="C335" s="8"/>
@@ -7715,27 +7682,38 @@
       </c>
     </row>
     <row r="336">
-      <c r="A336" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5700 - Post Production Sound</t>
-        </is>
-      </c>
-      <c r="B336" s="7"/>
-      <c r="C336" s="7"/>
-      <c r="D336" s="7"/>
-      <c r="E336" s="7"/>
-      <c r="F336" s="7"/>
-      <c r="G336" s="7"/>
+      <c r="A336" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3209</t>
+        </is>
+      </c>
+      <c r="B336" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Errors and omissions insurance</t>
+        </is>
+      </c>
+      <c r="C336" s="8"/>
+      <c r="D336" s="9">
+        <v>0</v>
+      </c>
+      <c r="E336" s="11"/>
+      <c r="F336" s="10">
+        <v>0</v>
+      </c>
+      <c r="G336" s="10">
+        <f>ROUND(D336*F336,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="337">
       <c r="A337" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5701</t>
+          <t xml:space="preserve">3212</t>
         </is>
       </c>
       <c r="B337" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound Package</t>
+          <t xml:space="preserve">Travel and medical insurance</t>
         </is>
       </c>
       <c r="C337" s="8"/>
@@ -7754,12 +7732,12 @@
     <row r="338">
       <c r="A338" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5702</t>
+          <t xml:space="preserve">3215</t>
         </is>
       </c>
       <c r="B338" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Crowd &amp; ADR Artistes</t>
+          <t xml:space="preserve">Risk assessments</t>
         </is>
       </c>
       <c r="C338" s="8"/>
@@ -7778,12 +7756,12 @@
     <row r="339">
       <c r="A339" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5705</t>
+          <t xml:space="preserve">3218</t>
         </is>
       </c>
       <c r="B339" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">ADR Stages</t>
+          <t xml:space="preserve">Health and safety adviser</t>
         </is>
       </c>
       <c r="C339" s="8"/>
@@ -7802,12 +7780,12 @@
     <row r="340">
       <c r="A340" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5706</t>
+          <t xml:space="preserve">3221</t>
         </is>
       </c>
       <c r="B340" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Foley Studio</t>
+          <t xml:space="preserve">Intimacy coordinator</t>
         </is>
       </c>
       <c r="C340" s="8"/>
@@ -7826,12 +7804,12 @@
     <row r="341">
       <c r="A341" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5715</t>
+          <t xml:space="preserve">3224</t>
         </is>
       </c>
       <c r="B341" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sound Transfers</t>
+          <t xml:space="preserve">Safeguarding support</t>
         </is>
       </c>
       <c r="C341" s="8"/>
@@ -7850,12 +7828,12 @@
     <row r="342">
       <c r="A342" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5719</t>
+          <t xml:space="preserve">3227</t>
         </is>
       </c>
       <c r="B342" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Temp Mix</t>
+          <t xml:space="preserve">Security assessment</t>
         </is>
       </c>
       <c r="C342" s="8"/>
@@ -7874,12 +7852,12 @@
     <row r="343">
       <c r="A343" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5725</t>
+          <t xml:space="preserve">3230</t>
         </is>
       </c>
       <c r="B343" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Final Dub/Mix</t>
+          <t xml:space="preserve">Emergency planning and drills</t>
         </is>
       </c>
       <c r="C343" s="8"/>
@@ -7896,51 +7874,51 @@
       </c>
     </row>
     <row r="344">
-      <c r="A344" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5740</t>
-        </is>
-      </c>
-      <c r="B344" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Laydown/Layback</t>
-        </is>
-      </c>
-      <c r="C344" s="8"/>
-      <c r="D344" s="9">
-        <v>0</v>
-      </c>
-      <c r="E344" s="11"/>
-      <c r="F344" s="10">
-        <v>0</v>
-      </c>
-      <c r="G344" s="10">
-        <f>ROUND(D344*F344,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A344" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3300 - Payroll, Employment &amp; Fringes</t>
+        </is>
+      </c>
+      <c r="B344" s="7"/>
+      <c r="C344" s="7"/>
+      <c r="D344" s="7"/>
+      <c r="E344" s="7"/>
+      <c r="F344" s="7"/>
+      <c r="G344" s="7"/>
     </row>
     <row r="345">
-      <c r="A345" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5800 - Post Film &amp; Lab</t>
-        </is>
-      </c>
-      <c r="B345" s="7"/>
-      <c r="C345" s="7"/>
-      <c r="D345" s="7"/>
-      <c r="E345" s="7"/>
-      <c r="F345" s="7"/>
-      <c r="G345" s="7"/>
+      <c r="A345" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3303</t>
+        </is>
+      </c>
+      <c r="B345" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Employer payroll charges</t>
+        </is>
+      </c>
+      <c r="C345" s="8"/>
+      <c r="D345" s="9">
+        <v>0</v>
+      </c>
+      <c r="E345" s="11"/>
+      <c r="F345" s="10">
+        <v>0</v>
+      </c>
+      <c r="G345" s="10">
+        <f>ROUND(D345*F345,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="346">
       <c r="A346" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5801</t>
+          <t xml:space="preserve">3306</t>
         </is>
       </c>
       <c r="B346" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Extraction &amp; Conform</t>
+          <t xml:space="preserve">Pension contributions</t>
         </is>
       </c>
       <c r="C346" s="8"/>
@@ -7959,12 +7937,12 @@
     <row r="347">
       <c r="A347" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5804</t>
+          <t xml:space="preserve">3309</t>
         </is>
       </c>
       <c r="B347" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Master Grade</t>
+          <t xml:space="preserve">Holiday pay</t>
         </is>
       </c>
       <c r="C347" s="8"/>
@@ -7983,12 +7961,12 @@
     <row r="348">
       <c r="A348" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5811</t>
+          <t xml:space="preserve">3312</t>
         </is>
       </c>
       <c r="B348" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Qar</t>
+          <t xml:space="preserve">Overtime premium allowance</t>
         </is>
       </c>
       <c r="C348" s="8"/>
@@ -8007,12 +7985,12 @@
     <row r="349">
       <c r="A349" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">5815</t>
+          <t xml:space="preserve">3315</t>
         </is>
       </c>
       <c r="B349" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Photomaterial</t>
+          <t xml:space="preserve">Meal penalties and turnaround costs</t>
         </is>
       </c>
       <c r="C349" s="8"/>
@@ -8029,27 +8007,38 @@
       </c>
     </row>
     <row r="350">
-      <c r="A350" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6100 - Visual Effects</t>
-        </is>
-      </c>
-      <c r="B350" s="7"/>
-      <c r="C350" s="7"/>
-      <c r="D350" s="7"/>
-      <c r="E350" s="7"/>
-      <c r="F350" s="7"/>
-      <c r="G350" s="7"/>
+      <c r="A350" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3318</t>
+        </is>
+      </c>
+      <c r="B350" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Union and guild costs</t>
+        </is>
+      </c>
+      <c r="C350" s="8"/>
+      <c r="D350" s="9">
+        <v>0</v>
+      </c>
+      <c r="E350" s="11"/>
+      <c r="F350" s="10">
+        <v>0</v>
+      </c>
+      <c r="G350" s="10">
+        <f>ROUND(D350*F350,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="351">
       <c r="A351" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6103</t>
+          <t xml:space="preserve">3321</t>
         </is>
       </c>
       <c r="B351" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Visual Effects Package</t>
+          <t xml:space="preserve">Payroll service fees</t>
         </is>
       </c>
       <c r="C351" s="8"/>
@@ -8066,27 +8055,38 @@
       </c>
     </row>
     <row r="352">
-      <c r="A352" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6200 - Delivery</t>
-        </is>
-      </c>
-      <c r="B352" s="7"/>
-      <c r="C352" s="7"/>
-      <c r="D352" s="7"/>
-      <c r="E352" s="7"/>
-      <c r="F352" s="7"/>
-      <c r="G352" s="7"/>
+      <c r="A352" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3324</t>
+        </is>
+      </c>
+      <c r="B352" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Work permits</t>
+        </is>
+      </c>
+      <c r="C352" s="8"/>
+      <c r="D352" s="9">
+        <v>0</v>
+      </c>
+      <c r="E352" s="11"/>
+      <c r="F352" s="10">
+        <v>0</v>
+      </c>
+      <c r="G352" s="10">
+        <f>ROUND(D352*F352,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="353">
       <c r="A353" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6235</t>
+          <t xml:space="preserve">3327</t>
         </is>
       </c>
       <c r="B353" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Deliverables</t>
+          <t xml:space="preserve">Training and apprenticeship levies</t>
         </is>
       </c>
       <c r="C353" s="8"/>
@@ -8103,38 +8103,27 @@
       </c>
     </row>
     <row r="354">
-      <c r="A354" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6245</t>
-        </is>
-      </c>
-      <c r="B354" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Audio Deliverables</t>
-        </is>
-      </c>
-      <c r="C354" s="8"/>
-      <c r="D354" s="9">
-        <v>0</v>
-      </c>
-      <c r="E354" s="11"/>
-      <c r="F354" s="10">
-        <v>0</v>
-      </c>
-      <c r="G354" s="10">
-        <f>ROUND(D354*F354,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A354" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3400 - Audit, Finance &amp; Corporate Costs</t>
+        </is>
+      </c>
+      <c r="B354" s="7"/>
+      <c r="C354" s="7"/>
+      <c r="D354" s="7"/>
+      <c r="E354" s="7"/>
+      <c r="F354" s="7"/>
+      <c r="G354" s="7"/>
     </row>
     <row r="355">
       <c r="A355" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6255</t>
+          <t xml:space="preserve">3403</t>
         </is>
       </c>
       <c r="B355" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">File Deliverables For Sub Vendors (A)</t>
+          <t xml:space="preserve">Production legal fees</t>
         </is>
       </c>
       <c r="C355" s="8"/>
@@ -8153,12 +8142,12 @@
     <row r="356">
       <c r="A356" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6265</t>
+          <t xml:space="preserve">3406</t>
         </is>
       </c>
       <c r="B356" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">File Deliverables For Sub Vendors (B)</t>
+          <t xml:space="preserve">Accounting and audit fees</t>
         </is>
       </c>
       <c r="C356" s="8"/>
@@ -8177,12 +8166,12 @@
     <row r="357">
       <c r="A357" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6275</t>
+          <t xml:space="preserve">3409</t>
         </is>
       </c>
       <c r="B357" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Alternative Version Scenes</t>
+          <t xml:space="preserve">Bank charges</t>
         </is>
       </c>
       <c r="C357" s="8"/>
@@ -8199,27 +8188,38 @@
       </c>
     </row>
     <row r="358">
-      <c r="A358" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6500 - Other</t>
-        </is>
-      </c>
-      <c r="B358" s="7"/>
-      <c r="C358" s="7"/>
-      <c r="D358" s="7"/>
-      <c r="E358" s="7"/>
-      <c r="F358" s="7"/>
-      <c r="G358" s="7"/>
+      <c r="A358" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3412</t>
+        </is>
+      </c>
+      <c r="B358" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Foreign exchange costs</t>
+        </is>
+      </c>
+      <c r="C358" s="8"/>
+      <c r="D358" s="9">
+        <v>0</v>
+      </c>
+      <c r="E358" s="11"/>
+      <c r="F358" s="10">
+        <v>0</v>
+      </c>
+      <c r="G358" s="10">
+        <f>ROUND(D358*F358,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="359">
       <c r="A359" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6502</t>
+          <t xml:space="preserve">3415</t>
         </is>
       </c>
       <c r="B359" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Review &amp; Notes</t>
+          <t xml:space="preserve">Financing fees and interest</t>
         </is>
       </c>
       <c r="C359" s="8"/>
@@ -8236,27 +8236,38 @@
       </c>
     </row>
     <row r="360">
-      <c r="A360" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6600 - Publicity</t>
-        </is>
-      </c>
-      <c r="B360" s="7"/>
-      <c r="C360" s="7"/>
-      <c r="D360" s="7"/>
-      <c r="E360" s="7"/>
-      <c r="F360" s="7"/>
-      <c r="G360" s="7"/>
+      <c r="A360" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3418</t>
+        </is>
+      </c>
+      <c r="B360" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Completion security</t>
+        </is>
+      </c>
+      <c r="C360" s="8"/>
+      <c r="D360" s="9">
+        <v>0</v>
+      </c>
+      <c r="E360" s="11"/>
+      <c r="F360" s="10">
+        <v>0</v>
+      </c>
+      <c r="G360" s="10">
+        <f>ROUND(D360*F360,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="361">
       <c r="A361" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6601</t>
+          <t xml:space="preserve">3421</t>
         </is>
       </c>
       <c r="B361" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Unit Publicity</t>
+          <t xml:space="preserve">Company administration</t>
         </is>
       </c>
       <c r="C361" s="8"/>
@@ -8275,12 +8286,12 @@
     <row r="362">
       <c r="A362" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6615</t>
+          <t xml:space="preserve">3424</t>
         </is>
       </c>
       <c r="B362" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Previews</t>
+          <t xml:space="preserve">Tax and incentive consultancy</t>
         </is>
       </c>
       <c r="C362" s="8"/>
@@ -8299,12 +8310,12 @@
     <row r="363">
       <c r="A363" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6685</t>
+          <t xml:space="preserve">3427</t>
         </is>
       </c>
       <c r="B363" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Stills Photographer</t>
+          <t xml:space="preserve">Production service fee</t>
         </is>
       </c>
       <c r="C363" s="8"/>
@@ -8321,38 +8332,27 @@
       </c>
     </row>
     <row r="364">
-      <c r="A364" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6694</t>
-        </is>
-      </c>
-      <c r="B364" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Trailer</t>
-        </is>
-      </c>
-      <c r="C364" s="8"/>
-      <c r="D364" s="9">
-        <v>0</v>
-      </c>
-      <c r="E364" s="11"/>
-      <c r="F364" s="10">
-        <v>0</v>
-      </c>
-      <c r="G364" s="10">
-        <f>ROUND(D364*F364,2)</f>
-        <v>0</v>
-      </c>
+      <c r="A364" s="7" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3500 - Production Technology, Security &amp; Sustainability</t>
+        </is>
+      </c>
+      <c r="B364" s="7"/>
+      <c r="C364" s="7"/>
+      <c r="D364" s="7"/>
+      <c r="E364" s="7"/>
+      <c r="F364" s="7"/>
+      <c r="G364" s="7"/>
     </row>
     <row r="365">
       <c r="A365" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6695</t>
+          <t xml:space="preserve">3503</t>
         </is>
       </c>
       <c r="B365" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">EPK</t>
+          <t xml:space="preserve">Production software</t>
         </is>
       </c>
       <c r="C365" s="8"/>
@@ -8369,27 +8369,38 @@
       </c>
     </row>
     <row r="366">
-      <c r="A366" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6700 - Insurance</t>
-        </is>
-      </c>
-      <c r="B366" s="7"/>
-      <c r="C366" s="7"/>
-      <c r="D366" s="7"/>
-      <c r="E366" s="7"/>
-      <c r="F366" s="7"/>
-      <c r="G366" s="7"/>
+      <c r="A366" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3506</t>
+        </is>
+      </c>
+      <c r="B366" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Digital collaboration tools</t>
+        </is>
+      </c>
+      <c r="C366" s="8"/>
+      <c r="D366" s="9">
+        <v>0</v>
+      </c>
+      <c r="E366" s="11"/>
+      <c r="F366" s="10">
+        <v>0</v>
+      </c>
+      <c r="G366" s="10">
+        <f>ROUND(D366*F366,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="367">
       <c r="A367" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6702</t>
+          <t xml:space="preserve">3509</t>
         </is>
       </c>
       <c r="B367" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Cast &amp; Crew Medicals</t>
+          <t xml:space="preserve">Cybersecurity review</t>
         </is>
       </c>
       <c r="C367" s="8"/>
@@ -8408,12 +8419,12 @@
     <row r="368">
       <c r="A368" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6703</t>
+          <t xml:space="preserve">3512</t>
         </is>
       </c>
       <c r="B368" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Errors &amp; Omissions</t>
+          <t xml:space="preserve">Secure file transfer</t>
         </is>
       </c>
       <c r="C368" s="8"/>
@@ -8432,12 +8443,12 @@
     <row r="369">
       <c r="A369" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6704</t>
+          <t xml:space="preserve">3515</t>
         </is>
       </c>
       <c r="B369" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Local Insurance</t>
+          <t xml:space="preserve">Identity and access management</t>
         </is>
       </c>
       <c r="C369" s="8"/>
@@ -8456,12 +8467,12 @@
     <row r="370">
       <c r="A370" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6705</t>
+          <t xml:space="preserve">3518</t>
         </is>
       </c>
       <c r="B370" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Production Insurance</t>
+          <t xml:space="preserve">Data protection support</t>
         </is>
       </c>
       <c r="C370" s="8"/>
@@ -8478,27 +8489,38 @@
       </c>
     </row>
     <row r="371">
-      <c r="A371" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6800 - General Expenses</t>
-        </is>
-      </c>
-      <c r="B371" s="7"/>
-      <c r="C371" s="7"/>
-      <c r="D371" s="7"/>
-      <c r="E371" s="7"/>
-      <c r="F371" s="7"/>
-      <c r="G371" s="7"/>
+      <c r="A371" s="11" t="inlineStr">
+        <is>
+          <t xml:space="preserve">3521</t>
+        </is>
+      </c>
+      <c r="B371" s="8" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Carbon measurement</t>
+        </is>
+      </c>
+      <c r="C371" s="8"/>
+      <c r="D371" s="9">
+        <v>0</v>
+      </c>
+      <c r="E371" s="11"/>
+      <c r="F371" s="10">
+        <v>0</v>
+      </c>
+      <c r="G371" s="10">
+        <f>ROUND(D371*F371,2)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="372">
       <c r="A372" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6803</t>
+          <t xml:space="preserve">3524</t>
         </is>
       </c>
       <c r="B372" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Legal Fees</t>
+          <t xml:space="preserve">Sustainability coordinator</t>
         </is>
       </c>
       <c r="C372" s="8"/>
@@ -8517,12 +8539,12 @@
     <row r="373">
       <c r="A373" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6806</t>
+          <t xml:space="preserve">3527</t>
         </is>
       </c>
       <c r="B373" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accountancy &amp; Audit Fee</t>
+          <t xml:space="preserve">Low-emission power and transport premium</t>
         </is>
       </c>
       <c r="C373" s="8"/>
@@ -8541,12 +8563,12 @@
     <row r="374">
       <c r="A374" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6808</t>
+          <t xml:space="preserve">3530</t>
         </is>
       </c>
       <c r="B374" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Work Permits</t>
+          <t xml:space="preserve">Reusable materials and waste reduction</t>
         </is>
       </c>
       <c r="C374" s="8"/>
@@ -8565,12 +8587,12 @@
     <row r="375">
       <c r="A375" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6809</t>
+          <t xml:space="preserve">3533</t>
         </is>
       </c>
       <c r="B375" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Accounts Software</t>
+          <t xml:space="preserve">Community engagement</t>
         </is>
       </c>
       <c r="C375" s="8"/>
@@ -8589,12 +8611,12 @@
     <row r="376">
       <c r="A376" s="11" t="inlineStr">
         <is>
-          <t xml:space="preserve">6810</t>
+          <t xml:space="preserve">3536</t>
         </is>
       </c>
       <c r="B376" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bank Charges</t>
+          <t xml:space="preserve">Environmental reporting</t>
         </is>
       </c>
       <c r="C376" s="8"/>
@@ -8610,282 +8632,84 @@
         <v>0</v>
       </c>
     </row>
-    <row r="377">
-      <c r="A377" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6811</t>
-        </is>
-      </c>
-      <c r="B377" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Financing</t>
-        </is>
-      </c>
-      <c r="C377" s="8"/>
-      <c r="D377" s="9">
-        <v>0</v>
-      </c>
-      <c r="E377" s="11"/>
-      <c r="F377" s="10">
-        <v>0</v>
-      </c>
-      <c r="G377" s="10">
-        <f>ROUND(D377*F377,2)</f>
-        <v>0</v>
-      </c>
-    </row>
+    <row r="377"/>
     <row r="378">
-      <c r="A378" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6813</t>
-        </is>
-      </c>
-      <c r="B378" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Archive Footage</t>
-        </is>
-      </c>
-      <c r="C378" s="8"/>
-      <c r="D378" s="9">
-        <v>0</v>
-      </c>
-      <c r="E378" s="11"/>
-      <c r="F378" s="10">
-        <v>0</v>
-      </c>
-      <c r="G378" s="10">
-        <f>ROUND(D378*F378,2)</f>
+      <c r="E378" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Total (excl. VAT)</t>
+        </is>
+      </c>
+      <c r="F378" s="12"/>
+      <c r="G378" s="13">
+        <f>SUM(G13:G376)</f>
         <v>0</v>
       </c>
     </row>
     <row r="379">
-      <c r="A379" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6815</t>
-        </is>
-      </c>
-      <c r="B379" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Production Services</t>
-        </is>
-      </c>
-      <c r="C379" s="8"/>
-      <c r="D379" s="9">
-        <v>0</v>
-      </c>
-      <c r="E379" s="11"/>
-      <c r="F379" s="10">
-        <v>0</v>
-      </c>
-      <c r="G379" s="10">
-        <f>ROUND(D379*F379,2)</f>
+      <c r="E379" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Contingency (%)</t>
+        </is>
+      </c>
+      <c r="F379" s="14">
+        <v>10</v>
+      </c>
+      <c r="G379" s="13">
+        <f>ROUND(G378*F379/100,2)</f>
         <v>0</v>
       </c>
     </row>
     <row r="380">
-      <c r="A380" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6885</t>
-        </is>
-      </c>
-      <c r="B380" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Other Cost</t>
-        </is>
-      </c>
-      <c r="C380" s="8"/>
-      <c r="D380" s="9">
-        <v>0</v>
-      </c>
-      <c r="E380" s="11"/>
-      <c r="F380" s="10">
-        <v>0</v>
-      </c>
-      <c r="G380" s="10">
-        <f>ROUND(D380*F380,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="381">
-      <c r="A381" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6898</t>
-        </is>
-      </c>
-      <c r="B381" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fringe</t>
-        </is>
-      </c>
-      <c r="C381" s="8"/>
-      <c r="D381" s="9">
-        <v>0</v>
-      </c>
-      <c r="E381" s="11"/>
-      <c r="F381" s="10">
-        <v>0</v>
-      </c>
-      <c r="G381" s="10">
-        <f>ROUND(D381*F381,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="382">
-      <c r="A382" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6900 - Completion Bond</t>
-        </is>
-      </c>
-      <c r="B382" s="7"/>
-      <c r="C382" s="7"/>
-      <c r="D382" s="7"/>
-      <c r="E382" s="7"/>
-      <c r="F382" s="7"/>
-      <c r="G382" s="7"/>
-    </row>
-    <row r="383">
-      <c r="A383" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6900</t>
-        </is>
-      </c>
-      <c r="B383" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Completion Bond</t>
-        </is>
-      </c>
-      <c r="C383" s="8"/>
-      <c r="D383" s="9">
-        <v>0</v>
-      </c>
-      <c r="E383" s="11"/>
-      <c r="F383" s="10">
-        <v>0</v>
-      </c>
-      <c r="G383" s="10">
-        <f>ROUND(D383*F383,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="384">
-      <c r="A384" s="7" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9500 - Titles</t>
-        </is>
-      </c>
-      <c r="B384" s="7"/>
-      <c r="C384" s="7"/>
-      <c r="D384" s="7"/>
-      <c r="E384" s="7"/>
-      <c r="F384" s="7"/>
-      <c r="G384" s="7"/>
-    </row>
-    <row r="385">
-      <c r="A385" s="11" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9500</t>
-        </is>
-      </c>
-      <c r="B385" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Titles</t>
-        </is>
-      </c>
-      <c r="C385" s="8"/>
-      <c r="D385" s="9">
-        <v>0</v>
-      </c>
-      <c r="E385" s="11"/>
-      <c r="F385" s="10">
-        <v>0</v>
-      </c>
-      <c r="G385" s="10">
-        <f>ROUND(D385*F385,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="386"/>
-    <row r="387">
-      <c r="E387" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Total (excl. VAT)</t>
-        </is>
-      </c>
-      <c r="F387" s="12"/>
-      <c r="G387" s="13">
-        <f>SUM(G13:G385)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="388">
-      <c r="E388" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Contingency (%)</t>
-        </is>
-      </c>
-      <c r="F388" s="14">
-        <v>10</v>
-      </c>
-      <c r="G388" s="13">
-        <f>ROUND(G387*F388/100,2)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="389">
-      <c r="E389" s="12" t="inlineStr">
+      <c r="E380" s="12" t="inlineStr">
         <is>
           <t xml:space="preserve">Total incl. additional costs</t>
         </is>
       </c>
-      <c r="F389" s="12"/>
-      <c r="G389" s="13">
-        <f>G387+G388</f>
+      <c r="F380" s="12"/>
+      <c r="G380" s="13">
+        <f>G378+G379</f>
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="41">
+  <mergeCells count="37">
     <mergeCell ref="A12:G12"/>
-    <mergeCell ref="A22:G22"/>
-    <mergeCell ref="A32:G32"/>
-    <mergeCell ref="A40:G40"/>
-    <mergeCell ref="A58:G58"/>
-    <mergeCell ref="A74:G74"/>
-    <mergeCell ref="A91:G91"/>
-    <mergeCell ref="A99:G99"/>
-    <mergeCell ref="A112:G112"/>
-    <mergeCell ref="A136:G136"/>
-    <mergeCell ref="A148:G148"/>
-    <mergeCell ref="A158:G158"/>
-    <mergeCell ref="A169:G169"/>
-    <mergeCell ref="A178:G178"/>
-    <mergeCell ref="A180:G180"/>
-    <mergeCell ref="A185:G185"/>
-    <mergeCell ref="A201:G201"/>
-    <mergeCell ref="A219:G219"/>
-    <mergeCell ref="A229:G229"/>
-    <mergeCell ref="A242:G242"/>
-    <mergeCell ref="A250:G250"/>
-    <mergeCell ref="A260:G260"/>
-    <mergeCell ref="A274:G274"/>
-    <mergeCell ref="A291:G291"/>
-    <mergeCell ref="A295:G295"/>
-    <mergeCell ref="A297:G297"/>
-    <mergeCell ref="A314:G314"/>
-    <mergeCell ref="A316:G316"/>
-    <mergeCell ref="A329:G329"/>
-    <mergeCell ref="A336:G336"/>
-    <mergeCell ref="A345:G345"/>
-    <mergeCell ref="A350:G350"/>
-    <mergeCell ref="A352:G352"/>
-    <mergeCell ref="A358:G358"/>
-    <mergeCell ref="A360:G360"/>
-    <mergeCell ref="A366:G366"/>
-    <mergeCell ref="A371:G371"/>
-    <mergeCell ref="A382:G382"/>
-    <mergeCell ref="A384:G384"/>
-    <mergeCell ref="E387:F387"/>
-    <mergeCell ref="E389:F389"/>
+    <mergeCell ref="A20:G20"/>
+    <mergeCell ref="A29:G29"/>
+    <mergeCell ref="A38:G38"/>
+    <mergeCell ref="A46:G46"/>
+    <mergeCell ref="A59:G59"/>
+    <mergeCell ref="A70:G70"/>
+    <mergeCell ref="A81:G81"/>
+    <mergeCell ref="A92:G92"/>
+    <mergeCell ref="A101:G101"/>
+    <mergeCell ref="A109:G109"/>
+    <mergeCell ref="A119:G119"/>
+    <mergeCell ref="A130:G130"/>
+    <mergeCell ref="A142:G142"/>
+    <mergeCell ref="A153:G153"/>
+    <mergeCell ref="A162:G162"/>
+    <mergeCell ref="A177:G177"/>
+    <mergeCell ref="A188:G188"/>
+    <mergeCell ref="A200:G200"/>
+    <mergeCell ref="A211:G211"/>
+    <mergeCell ref="A220:G220"/>
+    <mergeCell ref="A233:G233"/>
+    <mergeCell ref="A243:G243"/>
+    <mergeCell ref="A254:G254"/>
+    <mergeCell ref="A263:G263"/>
+    <mergeCell ref="A275:G275"/>
+    <mergeCell ref="A285:G285"/>
+    <mergeCell ref="A294:G294"/>
+    <mergeCell ref="A304:G304"/>
+    <mergeCell ref="A313:G313"/>
+    <mergeCell ref="A324:G324"/>
+    <mergeCell ref="A333:G333"/>
+    <mergeCell ref="A344:G344"/>
+    <mergeCell ref="A354:G354"/>
+    <mergeCell ref="A364:G364"/>
+    <mergeCell ref="E378:F378"/>
+    <mergeCell ref="E380:F380"/>
   </mergeCells>
 </worksheet>
 </file>
@@ -8910,7 +8734,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Generated: 17 September 2026</t>
+          <t xml:space="preserve">Generated: 23 October 2026</t>
         </is>
       </c>
     </row>
@@ -8940,721 +8764,649 @@
     <row r="5">
       <c r="A5" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1100 - Development, Story, Rights, Continuity</t>
+          <t xml:space="preserve">0100 - Development &amp; Research</t>
         </is>
       </c>
       <c r="B5" s="9">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="C5" s="10">
-        <f>SUM(Budget!G13:G21)</f>
+        <f>SUM(Budget!G13:G19)</f>
         <v>0</v>
       </c>
       <c r="D5" s="15">
-        <f>IF($C$45=0,0,C5/$C$45)</f>
+        <f>IF($C$41=0,0,C5/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200 - Producers</t>
+          <t xml:space="preserve">0200 - Rights, Clearances &amp; Archive</t>
         </is>
       </c>
       <c r="B6" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C6" s="10">
-        <f>SUM(Budget!G23:G31)</f>
+        <f>SUM(Budget!G21:G28)</f>
         <v>0</v>
       </c>
       <c r="D6" s="15">
-        <f>IF($C$45=0,0,C6/$C$45)</f>
+        <f>IF($C$41=0,0,C6/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1300 - Direction</t>
+          <t xml:space="preserve">0300 - Producing &amp; Business Affairs</t>
         </is>
       </c>
       <c r="B7" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C7" s="10">
-        <f>SUM(Budget!G33:G39)</f>
+        <f>SUM(Budget!G30:G37)</f>
         <v>0</v>
       </c>
       <c r="D7" s="15">
-        <f>IF($C$45=0,0,C7/$C$45)</f>
+        <f>IF($C$41=0,0,C7/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1400 - Cast</t>
+          <t xml:space="preserve">0400 - Directing &amp; Creative Leadership</t>
         </is>
       </c>
       <c r="B8" s="9">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="C8" s="10">
-        <f>SUM(Budget!G41:G57)</f>
+        <f>SUM(Budget!G39:G45)</f>
         <v>0</v>
       </c>
       <c r="D8" s="15">
-        <f>IF($C$45=0,0,C8/$C$45)</f>
+        <f>IF($C$41=0,0,C8/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">1500 - ATL Travel &amp; Living</t>
+          <t xml:space="preserve">0500 - Cast, Casting &amp; Performance</t>
         </is>
       </c>
       <c r="B9" s="9">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="10">
-        <f>SUM(Budget!G59:G73)</f>
+        <f>SUM(Budget!G47:G58)</f>
         <v>0</v>
       </c>
       <c r="D9" s="15">
-        <f>IF($C$45=0,0,C9/$C$45)</f>
+        <f>IF($C$41=0,0,C9/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2000 - Production Staff</t>
+          <t xml:space="preserve">0600 - Production Management &amp; Accounts</t>
         </is>
       </c>
       <c r="B10" s="9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C10" s="10">
-        <f>SUM(Budget!G75:G90)</f>
+        <f>SUM(Budget!G60:G69)</f>
         <v>0</v>
       </c>
       <c r="D10" s="15">
-        <f>IF($C$45=0,0,C10/$C$45)</f>
+        <f>IF($C$41=0,0,C10/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2100 - Extra Talent</t>
+          <t xml:space="preserve">0700 - Assistant Direction, Continuity &amp; Background</t>
         </is>
       </c>
       <c r="B11" s="9">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="C11" s="10">
-        <f>SUM(Budget!G92:G98)</f>
+        <f>SUM(Budget!G71:G80)</f>
         <v>0</v>
       </c>
       <c r="D11" s="15">
-        <f>IF($C$45=0,0,C11/$C$45)</f>
+        <f>IF($C$41=0,0,C11/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2200 - Art Department</t>
+          <t xml:space="preserve">0800 - Locations, Permits &amp; Site Services</t>
         </is>
       </c>
       <c r="B12" s="9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C12" s="10">
-        <f>SUM(Budget!G100:G111)</f>
+        <f>SUM(Budget!G82:G91)</f>
         <v>0</v>
       </c>
       <c r="D12" s="15">
-        <f>IF($C$45=0,0,C12/$C$45)</f>
+        <f>IF($C$41=0,0,C12/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2300 - Construction</t>
+          <t xml:space="preserve">0900 - Travel, Accommodation &amp; Daily Allowances</t>
         </is>
       </c>
       <c r="B13" s="9">
-        <v>23</v>
+        <v>8</v>
       </c>
       <c r="C13" s="10">
-        <f>SUM(Budget!G113:G135)</f>
+        <f>SUM(Budget!G93:G100)</f>
         <v>0</v>
       </c>
       <c r="D13" s="15">
-        <f>IF($C$45=0,0,C13/$C$45)</f>
+        <f>IF($C$41=0,0,C13/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2400 - Set Dressing</t>
+          <t xml:space="preserve">1000 - Studios, Offices &amp; Workshops</t>
         </is>
       </c>
       <c r="B14" s="9">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C14" s="10">
-        <f>SUM(Budget!G137:G147)</f>
+        <f>SUM(Budget!G102:G108)</f>
         <v>0</v>
       </c>
       <c r="D14" s="15">
-        <f>IF($C$45=0,0,C14/$C$45)</f>
+        <f>IF($C$41=0,0,C14/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2500 - Property</t>
+          <t xml:space="preserve">1100 - Art Direction &amp; Design</t>
         </is>
       </c>
       <c r="B15" s="9">
         <v>9</v>
       </c>
       <c r="C15" s="10">
-        <f>SUM(Budget!G149:G157)</f>
+        <f>SUM(Budget!G110:G118)</f>
         <v>0</v>
       </c>
       <c r="D15" s="15">
-        <f>IF($C$45=0,0,C15/$C$45)</f>
+        <f>IF($C$41=0,0,C15/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2600 - Picture Vehicles &amp; Animals</t>
+          <t xml:space="preserve">1200 - Construction, Scenic &amp; Greens</t>
         </is>
       </c>
       <c r="B16" s="9">
         <v>10</v>
       </c>
       <c r="C16" s="10">
-        <f>SUM(Budget!G159:G168)</f>
+        <f>SUM(Budget!G120:G129)</f>
         <v>0</v>
       </c>
       <c r="D16" s="15">
-        <f>IF($C$45=0,0,C16/$C$45)</f>
+        <f>IF($C$41=0,0,C16/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2700 - Special Effects</t>
+          <t xml:space="preserve">1300 - Set Decoration, Props &amp; Graphics</t>
         </is>
       </c>
       <c r="B17" s="9">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="C17" s="10">
-        <f>SUM(Budget!G170:G177)</f>
+        <f>SUM(Budget!G131:G141)</f>
         <v>0</v>
       </c>
       <c r="D17" s="15">
-        <f>IF($C$45=0,0,C17/$C$45)</f>
+        <f>IF($C$41=0,0,C17/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2800 - Tests</t>
+          <t xml:space="preserve">1400 - Costume &amp; Wardrobe</t>
         </is>
       </c>
       <c r="B18" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C18" s="10">
-        <f>SUM(Budget!G179:G179)</f>
+        <f>SUM(Budget!G143:G152)</f>
         <v>0</v>
       </c>
       <c r="D18" s="15">
-        <f>IF($C$45=0,0,C18/$C$45)</f>
+        <f>IF($C$41=0,0,C18/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900 - Stages, Offices &amp; Workshops</t>
+          <t xml:space="preserve">1500 - Hair, Makeup &amp; Prosthetics</t>
         </is>
       </c>
       <c r="B19" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C19" s="10">
-        <f>SUM(Budget!G181:G184)</f>
+        <f>SUM(Budget!G154:G161)</f>
         <v>0</v>
       </c>
       <c r="D19" s="15">
-        <f>IF($C$45=0,0,C19/$C$45)</f>
+        <f>IF($C$41=0,0,C19/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3000 - Camera</t>
+          <t xml:space="preserve">1600 - Camera &amp; Imaging</t>
         </is>
       </c>
       <c r="B20" s="9">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="C20" s="10">
-        <f>SUM(Budget!G186:G200)</f>
+        <f>SUM(Budget!G163:G176)</f>
         <v>0</v>
       </c>
       <c r="D20" s="15">
-        <f>IF($C$45=0,0,C20/$C$45)</f>
+        <f>IF($C$41=0,0,C20/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3100 - Grips &amp; Set Operations</t>
+          <t xml:space="preserve">1700 - Lighting &amp; Electrical</t>
         </is>
       </c>
       <c r="B21" s="9">
-        <v>17</v>
+        <v>10</v>
       </c>
       <c r="C21" s="10">
-        <f>SUM(Budget!G202:G218)</f>
+        <f>SUM(Budget!G178:G187)</f>
         <v>0</v>
       </c>
       <c r="D21" s="15">
-        <f>IF($C$45=0,0,C21/$C$45)</f>
+        <f>IF($C$41=0,0,C21/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3200 - Electrical</t>
+          <t xml:space="preserve">1800 - Grip, Rigging &amp; Camera Movement</t>
         </is>
       </c>
       <c r="B22" s="9">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C22" s="10">
-        <f>SUM(Budget!G220:G228)</f>
+        <f>SUM(Budget!G189:G199)</f>
         <v>0</v>
       </c>
       <c r="D22" s="15">
-        <f>IF($C$45=0,0,C22/$C$45)</f>
+        <f>IF($C$41=0,0,C22/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3300 - Wardrobe</t>
+          <t xml:space="preserve">1900 - Production Sound &amp; Communications</t>
         </is>
       </c>
       <c r="B23" s="9">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C23" s="10">
-        <f>SUM(Budget!G230:G241)</f>
+        <f>SUM(Budget!G201:G210)</f>
         <v>0</v>
       </c>
       <c r="D23" s="15">
-        <f>IF($C$45=0,0,C23/$C$45)</f>
+        <f>IF($C$41=0,0,C23/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3400 - Make-Up &amp; Hairdressing</t>
+          <t xml:space="preserve">2000 - Data, Dailies &amp; Media</t>
         </is>
       </c>
       <c r="B24" s="9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C24" s="10">
-        <f>SUM(Budget!G243:G249)</f>
+        <f>SUM(Budget!G212:G219)</f>
         <v>0</v>
       </c>
       <c r="D24" s="15">
-        <f>IF($C$45=0,0,C24/$C$45)</f>
+        <f>IF($C$41=0,0,C24/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3500 - Sound &amp; Video</t>
+          <t xml:space="preserve">2100 - Transport &amp; Logistics</t>
         </is>
       </c>
       <c r="B25" s="9">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C25" s="10">
-        <f>SUM(Budget!G251:G259)</f>
+        <f>SUM(Budget!G221:G232)</f>
         <v>0</v>
       </c>
       <c r="D25" s="15">
-        <f>IF($C$45=0,0,C25/$C$45)</f>
+        <f>IF($C$41=0,0,C25/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3600 - Transportation</t>
+          <t xml:space="preserve">2200 - Catering, Welfare &amp; Unit Services</t>
         </is>
       </c>
       <c r="B26" s="9">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="C26" s="10">
-        <f>SUM(Budget!G261:G273)</f>
+        <f>SUM(Budget!G234:G242)</f>
         <v>0</v>
       </c>
       <c r="D26" s="15">
-        <f>IF($C$45=0,0,C26/$C$45)</f>
+        <f>IF($C$41=0,0,C26/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3700 - Locations &amp; BTL Travel/Living</t>
+          <t xml:space="preserve">2300 - Stunts, Animals &amp; Physical Effects</t>
         </is>
       </c>
       <c r="B27" s="9">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="C27" s="10">
-        <f>SUM(Budget!G275:G290)</f>
+        <f>SUM(Budget!G244:G253)</f>
         <v>0</v>
       </c>
       <c r="D27" s="15">
-        <f>IF($C$45=0,0,C27/$C$45)</f>
+        <f>IF($C$41=0,0,C27/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3800 - Digital Media &amp; Stock</t>
+          <t xml:space="preserve">2400 - Specialist Units &amp; Remote Capture</t>
         </is>
       </c>
       <c r="B28" s="9">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="C28" s="10">
-        <f>SUM(Budget!G292:G294)</f>
+        <f>SUM(Budget!G255:G262)</f>
         <v>0</v>
       </c>
       <c r="D28" s="15">
-        <f>IF($C$45=0,0,C28/$C$45)</f>
+        <f>IF($C$41=0,0,C28/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">3900 - Additional Hours</t>
+          <t xml:space="preserve">2500 - Editorial &amp; Post Management</t>
         </is>
       </c>
       <c r="B29" s="9">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C29" s="10">
-        <f>SUM(Budget!G296:G296)</f>
+        <f>SUM(Budget!G264:G274)</f>
         <v>0</v>
       </c>
       <c r="D29" s="15">
-        <f>IF($C$45=0,0,C29/$C$45)</f>
+        <f>IF($C$41=0,0,C29/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4000 - 2nd Unit</t>
+          <t xml:space="preserve">2600 - Post Sound &amp; Voice Recording</t>
         </is>
       </c>
       <c r="B30" s="9">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C30" s="10">
-        <f>SUM(Budget!G298:G313)</f>
+        <f>SUM(Budget!G276:G284)</f>
         <v>0</v>
       </c>
       <c r="D30" s="15">
-        <f>IF($C$45=0,0,C30/$C$45)</f>
+        <f>IF($C$41=0,0,C30/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">4100 - Special Units</t>
+          <t xml:space="preserve">2700 - Music &amp; Music Rights</t>
         </is>
       </c>
       <c r="B31" s="9">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="C31" s="10">
-        <f>SUM(Budget!G315:G315)</f>
+        <f>SUM(Budget!G286:G293)</f>
         <v>0</v>
       </c>
       <c r="D31" s="15">
-        <f>IF($C$45=0,0,C31/$C$45)</f>
+        <f>IF($C$41=0,0,C31/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5500 - Editing</t>
+          <t xml:space="preserve">2800 - VFX, Animation &amp; Motion Graphics</t>
         </is>
       </c>
       <c r="B32" s="9">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C32" s="10">
-        <f>SUM(Budget!G317:G328)</f>
+        <f>SUM(Budget!G295:G303)</f>
         <v>0</v>
       </c>
       <c r="D32" s="15">
-        <f>IF($C$45=0,0,C32/$C$45)</f>
+        <f>IF($C$41=0,0,C32/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5600 - Music</t>
+          <t xml:space="preserve">2900 - Colour, Finishing &amp; Mastering</t>
         </is>
       </c>
       <c r="B33" s="9">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="C33" s="10">
-        <f>SUM(Budget!G330:G335)</f>
+        <f>SUM(Budget!G305:G312)</f>
         <v>0</v>
       </c>
       <c r="D33" s="15">
-        <f>IF($C$45=0,0,C33/$C$45)</f>
+        <f>IF($C$41=0,0,C33/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5700 - Post Production Sound</t>
+          <t xml:space="preserve">3000 - Deliverables, Access &amp; Localisation</t>
         </is>
       </c>
       <c r="B34" s="9">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C34" s="10">
-        <f>SUM(Budget!G337:G344)</f>
+        <f>SUM(Budget!G314:G323)</f>
         <v>0</v>
       </c>
       <c r="D34" s="15">
-        <f>IF($C$45=0,0,C34/$C$45)</f>
+        <f>IF($C$41=0,0,C34/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">5800 - Post Film &amp; Lab</t>
+          <t xml:space="preserve">3100 - Publicity, Stills &amp; Audience Materials</t>
         </is>
       </c>
       <c r="B35" s="9">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="C35" s="10">
-        <f>SUM(Budget!G346:G349)</f>
+        <f>SUM(Budget!G325:G332)</f>
         <v>0</v>
       </c>
       <c r="D35" s="15">
-        <f>IF($C$45=0,0,C35/$C$45)</f>
+        <f>IF($C$41=0,0,C35/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6100 - Visual Effects</t>
+          <t xml:space="preserve">3200 - Insurance, Safety &amp; Risk</t>
         </is>
       </c>
       <c r="B36" s="9">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="C36" s="10">
-        <f>SUM(Budget!G351:G351)</f>
+        <f>SUM(Budget!G334:G343)</f>
         <v>0</v>
       </c>
       <c r="D36" s="15">
-        <f>IF($C$45=0,0,C36/$C$45)</f>
+        <f>IF($C$41=0,0,C36/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6200 - Delivery</t>
+          <t xml:space="preserve">3300 - Payroll, Employment &amp; Fringes</t>
         </is>
       </c>
       <c r="B37" s="9">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C37" s="10">
-        <f>SUM(Budget!G353:G357)</f>
+        <f>SUM(Budget!G345:G353)</f>
         <v>0</v>
       </c>
       <c r="D37" s="15">
-        <f>IF($C$45=0,0,C37/$C$45)</f>
+        <f>IF($C$41=0,0,C37/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6500 - Other</t>
+          <t xml:space="preserve">3400 - Audit, Finance &amp; Corporate Costs</t>
         </is>
       </c>
       <c r="B38" s="9">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="C38" s="10">
-        <f>SUM(Budget!G359:G359)</f>
+        <f>SUM(Budget!G355:G363)</f>
         <v>0</v>
       </c>
       <c r="D38" s="15">
-        <f>IF($C$45=0,0,C38/$C$45)</f>
+        <f>IF($C$41=0,0,C38/$C$41)</f>
         <v>0</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">6600 - Publicity</t>
+          <t xml:space="preserve">3500 - Production Technology, Security &amp; Sustainability</t>
         </is>
       </c>
       <c r="B39" s="9">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="C39" s="10">
-        <f>SUM(Budget!G361:G365)</f>
+        <f>SUM(Budget!G365:G376)</f>
         <v>0</v>
       </c>
       <c r="D39" s="15">
-        <f>IF($C$45=0,0,C39/$C$45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6700 - Insurance</t>
-        </is>
-      </c>
-      <c r="B40" s="9">
-        <v>4</v>
-      </c>
-      <c r="C40" s="10">
-        <f>SUM(Budget!G367:G370)</f>
-        <v>0</v>
-      </c>
-      <c r="D40" s="15">
-        <f>IF($C$45=0,0,C40/$C$45)</f>
-        <v>0</v>
-      </c>
-    </row>
+        <f>IF($C$41=0,0,C39/$C$41)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40"/>
     <row r="41">
-      <c r="A41" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6800 - General Expenses</t>
-        </is>
-      </c>
-      <c r="B41" s="9">
-        <v>10</v>
-      </c>
-      <c r="C41" s="10">
-        <f>SUM(Budget!G372:G381)</f>
+      <c r="A41" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TOTAL</t>
+        </is>
+      </c>
+      <c r="B41" s="13">
+        <v>330</v>
+      </c>
+      <c r="C41" s="13">
+        <f>SUM(C5:C39)</f>
         <v>0</v>
       </c>
       <c r="D41" s="15">
-        <f>IF($C$45=0,0,C41/$C$45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6900 - Completion Bond</t>
-        </is>
-      </c>
-      <c r="B42" s="9">
-        <v>1</v>
-      </c>
-      <c r="C42" s="10">
-        <f>SUM(Budget!G383:G383)</f>
-        <v>0</v>
-      </c>
-      <c r="D42" s="15">
-        <f>IF($C$45=0,0,C42/$C$45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9500 - Titles</t>
-        </is>
-      </c>
-      <c r="B43" s="9">
-        <v>1</v>
-      </c>
-      <c r="C43" s="10">
-        <f>SUM(Budget!G385:G385)</f>
-        <v>0</v>
-      </c>
-      <c r="D43" s="15">
-        <f>IF($C$45=0,0,C43/$C$45)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44"/>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t xml:space="preserve">TOTAL</t>
-        </is>
-      </c>
-      <c r="B45" s="13">
-        <v>335</v>
-      </c>
-      <c r="C45" s="13">
-        <f>SUM(C5:C43)</f>
-        <v>0</v>
-      </c>
-      <c r="D45" s="15">
-        <f>IF($C$45=0,0,1)</f>
+        <f>IF($C$41=0,0,1)</f>
         <v>0</v>
       </c>
     </row>
